--- a/IG/AI Native-AWS_IG.xlsx
+++ b/IG/AI Native-AWS_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8290954-4AC7-4B02-B99D-9C29D39467F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E88966D-4F71-411A-B4F1-DD0C3192B991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,29 +639,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>生成AIの活用が進む中、クラウドサービスへの支出額は世界的に増加傾向にある。
-特に、Amazon、Microsoft、Googleの3社で市場シェアの約7割を占めており、その中でもAmazonは市場シェア・案件数の両面でリーダー的な位置付けとなっている。
-また日本においても、これら3社に加えてOracleやさくらインターネットがガバメントクラウドに採用されたことで、官公庁や自治体システムのクラウド移行が加速している。
-これにより、クラウドサービスの重要性は今後さらに高まると考えられる。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>■オンプレミス
-サーバーやネットワーク機器、データベースなどのITリソースを自社内のデータセンター等に設置し、構築から運用・保守までを自社で管理する形態。
-システム構成やセキュリティ対策を自社の方針に合わせて自由に設計でき、アクセス制御やログ管理なども細かく調整できる。
-■クラウド
-外部のクラウドサービス事業者が提供するITリソースを、ネットワーク経由で利用する形態。
-自社でハードウェアを保有する必要がなく、必要な時に必要な分だけ利用できるため、初期費用を抑えつつ短期間で導入できる。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>■オンプレミスの場合
-サーバーを1台設置するだけでも、その周辺に多数のハードウェア機器や設備が必要となるため、初期コストおよび運用コストが非常に高くなる。
-■クラウドの場合
-機器や設備を自社で用意する必要がないため、初期投資を大幅に抑えることができ、結果としてコスト削減につながる。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>■俊敏性（アジリティ）
 ・オンプレミスの場合
 　自社でデータセンターの確保から機器調達、設置、構築までを行う必要があるため、利用開始までに数か月単位の時間がかかる。
@@ -723,22 +700,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>■Web3層構造（Web3層アーキテクチャ）
-Web3層構造とは、Webアプリケーションを以下の3つの層に分割して設計・構築するシステム構造のことである。
-　・プレゼンテーション層（画面・UI）
-　・アプリケーション層（業務ロジック）
-　・データ層（データベース）
-■3層分離
-　3層分離とは、Webアプリケーションを設計する際に、上記3つの層を分離して管理する設計手法を指す。
-■メリット
-　3層を分離することで、各層が独立して機能できるため、他の層に影響を与えずに変更やスケールが可能となる。
-　その結果、以下のような利点がある。
-　　・柔軟性の向上
-　　・セキュリティの向上
-　　・保守・管理の容易化</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-01
 </t>
     <phoneticPr fontId="3"/>
@@ -756,26 +717,6 @@
   <si>
     <t xml:space="preserve">・AI-01
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Amazon VPCは、ユーザーごとに論理的に分離された仮想ネットワーク環境である。
-オンプレミス環境における「DMZ（非武装地帯）」や「イントラネット（社内ネットワーク）」に相当する概念として扱われる。VPCはリージョン単位で作成され、その中に複数のアベイラビリティゾーン（AZ）を配置することができる。さらに各AZ内で、パブリックサブネットやプライベートサブネットに分割してネットワークを設計することが可能である。
-■階層構造の関係
-　リージョン ＞ VPC ＞ アベイラビリティゾーン（AZ） ＞ サブネット ＞ リソース（EC2など）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Elastic Load Balancing（ELB）は、複数のEC2インスタンスなどに対してアクセスを分散し、システム全体の負荷を最適化するサービスである。
-※オンプレミスにおける「ロードバランサー（負荷分散装置）」に相当する。
-■種類
-用途に応じて以下の3種類から選択できる。
-・ALB（Application Load Balancer）：HTTP/HTTPSなどアプリケーション層向け
-・NLB（Network Load Balancer）：TCP/UDPなど高性能・低遅延向け
-・GWLB（Gateway Load Balancer）：ネットワークアプライアンス連携向け
-■可用性・スケーラビリティ
-ELBは複数のアベイラビリティゾーン（AZ）にまたがって配置できるため、高い耐障害性を持つ。
-また、アクセス量に応じて自動的にキャパシティが増減し、負荷状況に応じたスケーリングが可能である。</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -797,42 +738,6 @@
 　従量課金制であり、低コストで利用可能（例：1GBあたり約数円/月程度）。
 ■連携性
 　他のAWSサービス（EC2、Lambda、CloudFrontなど）と柔軟に連携でき、幅広い用途で利用される。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>■オンプレミスの場合
-　データベースの構築・運用・保守はすべてユーザ側の責任となる。
-一方AWSでは、利用形態によって責任範囲が異なる。
-■EC2上にデータベースを構築する場合（IaaS）
-　EC2（仮想サーバー）上にデータベースを構築する場合、インフラ部分はAWSが責任を持つ一方で、OS・ミドルウェア・　データベースの運用はユーザ側の責任となる。
-　そのため、責任はAWSとユーザで分担される形となる。
-■Amazon RDSを利用する場合（マネージドサービス）
-　Amazon RDSを利用することで、データベースの運用管理の多くがAWS側に移譲される。
-　これによりユーザ側の責任範囲は主に「アプリケーション層」と「データ管理」に限定される。
-このように、マネージドサービスを利用することでユーザの運用負担を大幅に削減できる。これがクラウドにおけるマネージドサービスの大きな特徴であり、システム構築において推奨される理由である。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Amazon RDSは、クラウド上で提供されるマネージド型のリレーショナルデータベースサービスであり、オンプレミスにおける「リレーショナルデータベースサーバー」に相当する。
-MySQL、Oracle、SQL Server、PostgreSQL、MariaDB、Auroraなどの主要なデータベースエンジンから選択して利用できる。
-■可用性・耐障害性
-　待機系（スタンバイ）を複数のアベイラビリティゾーン（AZ）に分散配置することで、障害発生時でも自動的にフェイルオーバーし、高い可用性を実現できる。
-■運用・保守の効率化
-　以下の機能により、運用負荷とコストを削減できる。
-　　・自動バックアップ
-　　・パッチ適用の自動化
-　　・監視・メンテナンスの簡素化</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Amazon EC2は、クラウド上で提供される仮想サーバーサービスであり、オンプレミスにおける「物理サーバー」に相当する。
-仮想サーバーとは、1台の物理サーバーを論理的に分割し、複数のサーバーとして独立して利用できる仕組みである。
-EC2は数分で起動でき、利用した分だけ課金される従量課金モデル（秒単位課金など）で提供される。
-また、WindowsやLinuxなど複数のOSに対応しており、必要なソフトウェアを自由にインストールして利用できる。
-さらに、利用状況に応じて以下のような柔軟な変更が可能である。
-　・スケールアップ／ダウン（性能の変更）
-　・スケールアウト／イン（台数の増減）
-　・オートスケーリング（自動調整）</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -958,23 +863,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>■主要パブリッククラウド3社の特徴まとめ
-　現在の主要パブリッククラウドサービスであるAmazon Web Services（AWS）、Microsoft Azure、Google Cloudは、それぞれ強みの分野が異なる。
-■Amazon Web Services（AWS）
-　AWSはサービス数が非常に多く、機能の豊富さとグローバル展開に強みを持つ。
-　また、セキュリティと信頼性が高く、あらゆる業種・規模のシステムに対応できる総合型クラウドである。
-コスト最適化の選択肢も豊富で、最も汎用性の高いクラウドといえる。
-■Microsoft Azure
-　AzureはMicrosoft製品（Windows Server、Active Directory、Microsoft 365など）との親和性が高い点が最大の特徴である。
-　オンプレミス環境との連携（ハイブリッドクラウド）にも強く、企業システムとの統合に適している。
-また、AI・データ分析分野にも強みを持つ。
-■Google Cloud
-　Google Cloudはデータ分析とAI・機械学習領域に強みを持つクラウドである。
-　BigQueryやVertex AIなどの先進的なサービスが充実しており、データ活用や分析基盤として高く評価されている。
-また、Kubernetesの開発元としてコンテナ技術にも強い。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>　IaC（Infrastructure as Code）とは、クラウドが提供するツールを用いて、サーバーやネットワークなどのインフラ構成をコードとして記述し、環境構築や管理を自動化する仕組みである。
 　これにより、手作業ではなくコードベースでインフラを再現可能にし、環境構築の効率化や品質向上を実現する。
 ■マネジメントコンソール・CLIとの比較
@@ -1216,13 +1104,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>Amazon 〇〇：AWS初期から存在するサービスに多い。
-AWS △△：比較的新しいサービスに多い。
-接頭語なし：Fargate、Glue、Athena などがある。
-厳密な命名ルールがあるわけではなく、サービスごとのブランド戦略や登場時期によって決められている。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>★アプリケーションのリファクタリング
 ■モノリスの分解
  信頼性やパフォーマンスに課題があり、複数の機能が密結合したモノリシックアプリケーションを特定する。
@@ -1276,6 +1157,145 @@
   </si>
   <si>
     <t>AI Native-AWS</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　生成AIの活用が進む中、クラウドサービスへの支出額は世界的に増加傾向にある。
+　特に、Amazon、Microsoft、Googleの3社で市場シェアの約7割を占めており、その中でもAmazonは市場シェア・案件数の両面でリーダー的な位置付けとなっている。
+　また日本においても、これら3社に加えてOracleやさくらインターネットがガバメントクラウドに採用されたことで、官公庁や自治体システムのクラウド移行が加速している。
+　これにより、クラウドサービスの重要性は今後さらに高まると考えられる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>■オンプレミス
+　サーバーやネットワーク機器、データベースなどのITリソースを自社内のデータセンター等に設置し、構築から運用・保守までを自社で管理する形態。
+　システム構成やセキュリティ対策を自社の方針に合わせて自由に設計でき、アクセス制御やログ管理なども細かく調整できる。
+■クラウド
+　外部のクラウドサービス事業者が提供するITリソースを、ネットワーク経由で利用する形態。
+　自社でハードウェアを保有する必要がなく、必要な時に必要な分だけ利用できるため、初期費用を抑えつつ短期間で導入できる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>■オンプレミスの場合
+　サーバーを1台設置するだけでも、その周辺に多数のハードウェア機器や設備が必要となるため、初期コストおよび運用コストが非常に高くなる。
+■クラウドの場合
+　機器や設備を自社で用意する必要がないため、初期投資を大幅に抑えることができ、結果としてコスト削減につながる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　Amazon EC2は、クラウド上で提供される仮想サーバーサービスであり、オンプレミスにおける「物理サーバー」に相当する。
+　仮想サーバーとは、1台の物理サーバーを論理的に分割し、複数のサーバーとして独立して利用できる仕組みである。
+　EC2は数分で起動でき、利用した分だけ課金される従量課金モデル（秒単位課金など）で提供される。
+　また、WindowsやLinuxなど複数のOSに対応しており、必要なソフトウェアを自由にインストールして利用できる。
+　さらに、利用状況に応じて以下のような柔軟な変更が可能である。
+　・スケールアップ／ダウン（性能の変更）
+　・スケールアウト／イン（台数の増減）
+　・オートスケーリング（自動調整）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　Amazon RDSは、クラウド上で提供されるマネージド型のリレーショナルデータベースサービスであり、オンプレミスにおける「リレーショナルデータベースサーバー」に相当する。
+　MySQL、Oracle、SQL Server、PostgreSQL、MariaDB、Auroraなどの主要なデータベースエンジンから選択して利用できる。
+■可用性・耐障害性
+　待機系（スタンバイ）を複数のアベイラビリティゾーン（AZ）に分散配置することで、障害発生時でも自動的にフェイルオーバーし、高い可用性を実現できる。
+■運用・保守の効率化
+　以下の機能により、運用負荷とコストを削減できる。
+　　・自動バックアップ
+　　・パッチ適用の自動化
+　　・監視・メンテナンスの簡素化</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>■オンプレミスの場合
+　データベースの構築・運用・保守はすべてユーザ側の責任となる。
+　一方AWSでは、利用形態によって責任範囲が異なる。
+■EC2上にデータベースを構築する場合（IaaS）
+　EC2（仮想サーバー）上にデータベースを構築する場合、インフラ部分はAWSが責任を持つ一方で、OS・ミドルウェア・　データベースの運用はユーザ側の責任となる。
+　そのため、責任はAWSとユーザで分担される形となる。
+■Amazon RDSを利用する場合（マネージドサービス）
+　Amazon RDSを利用することで、データベースの運用管理の多くがAWS側に移譲される。
+　これによりユーザ側の責任範囲は主に「アプリケーション層」と「データ管理」に限定される。
+　このように、マネージドサービスを利用することでユーザの運用負担を大幅に削減できる。これがクラウドにおけるマネージドサービスの大きな特徴であり、システム構築において推奨される理由である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　Elastic Load Balancing（ELB）は、複数のEC2インスタンスなどに対してアクセスを分散し、システム全体の負荷を最適化するサービスである。
+※オンプレミスにおける「ロードバランサー（負荷分散装置）」に相当する。
+■種類
+　用途に応じて以下の3種類から選択できる。
+　・ALB（Application Load Balancer）：HTTP/HTTPSなどアプリケーション層向け
+　・NLB（Network Load Balancer）：TCP/UDPなど高性能・低遅延向け
+　・GWLB（Gateway Load Balancer）：ネットワークアプライアンス連携向け
+■可用性・スケーラビリティ
+　ELBは複数のアベイラビリティゾーン（AZ）にまたがって配置できるため、高い耐障害性を持つ。
+　また、アクセス量に応じて自動的にキャパシティが増減し、負荷状況に応じたスケーリングが可能である。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>　Amazon VPCは、ユーザーごとに論理的に分離された仮想ネットワーク環境である。
+　オンプレミス環境における「DMZ（非武装地帯）」や「イントラネット（社内ネットワーク）」に相当する概念として扱われる。
+　VPCはリージョン単位で作成され、その中に複数のアベイラビリティゾーン（AZ）を配置することができる。さらに各AZ内で、パブリックサブネットやプライベートサブネットに分割してネットワークを設計することが可能である。
+■階層構造の関係
+　リージョン ＞ VPC ＞ アベイラビリティゾーン（AZ） ＞ サブネット ＞ リソース（EC2など）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>■Web3層構造（Web3層アーキテクチャ）
+　Web3層構造とは、Webアプリケーションを以下の3つの層に分割して設計・構築するシステム構造のことである。
+　　・プレゼンテーション層（画面・UI）
+　　・アプリケーション層（業務ロジック）
+　　・データ層（データベース）
+■3層分離
+　3層分離とは、Webアプリケーションを設計する際に、上記3つの層を分離して管理する設計手法を指す。
+■メリット
+　3層を分離することで、各層が独立して機能できるため、他の層に影響を与えずに変更やスケールが可能となる。
+　その結果、以下のような利点がある。
+　　・柔軟性の向上
+　　・セキュリティの向上
+　　・保守・管理の容易化</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>■主要パブリッククラウド3社の特徴まとめ
+　現在の主要パブリッククラウドサービスであるAmazon Web Services（AWS）、Microsoft Azure、Google Cloudは、それぞれ強みの分野が異なる。
+■Amazon Web Services（AWS）
+　AWSはサービス数が非常に多く、機能の豊富さとグローバル展開に強みを持つ。
+　また、セキュリティと信頼性が高く、あらゆる業種・規模のシステムに対応できる総合型クラウドである。
+　コスト最適化の選択肢も豊富で、最も汎用性の高いクラウドといえる。
+■Microsoft Azure
+　AzureはMicrosoft製品（Windows Server、Active Directory、Microsoft 365など）との親和性が高い点が最大の特徴である。
+　オンプレミス環境との連携（ハイブリッドクラウド）にも強く、企業システムとの統合に適している。
+　また、AI・データ分析分野にも強みを持つ。
+■Google Cloud
+　Google Cloudはデータ分析とAI・機械学習領域に強みを持つクラウドである。
+　BigQueryやVertex AIなどの先進的なサービスが充実しており、データ活用や分析基盤として高く評価されている。
+　また、Kubernetesの開発元としてコンテナ技術にも強い。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下は解答です。
+Amazon 〇〇：AWS初期から存在するサービスに多い。
+AWS △△：比較的新しいサービスに多い。
+接頭語なし：Fargate、Glue、Athena などがある。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※厳密な命名ルールがあるわけではなく、サービスごとのブランド戦略や登場時期によって決められている。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイトウ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1979,6 +1999,15 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1996,15 +2025,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3078,30 +3098,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
       <c r="L5" s="32"/>
       <c r="M5" s="33"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="105"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
       <c r="L6" s="32"/>
       <c r="M6" s="33"/>
     </row>
@@ -3223,10 +3243,10 @@
       <c r="H13" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="103" t="s">
+      <c r="I13" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="104"/>
+      <c r="J13" s="98"/>
       <c r="K13" s="87" t="s">
         <v>34</v>
       </c>
@@ -3256,7 +3276,7 @@
     </row>
     <row r="15" spans="1:14" ht="88.2">
       <c r="A15" s="10"/>
-      <c r="B15" s="100" t="str">
+      <c r="B15" s="103" t="str">
         <f>master!B4</f>
         <v>クラウドとは？</v>
       </c>
@@ -3264,11 +3284,11 @@
         <f>master!C4</f>
         <v>１．IT業界の歴史</v>
       </c>
-      <c r="D15" s="97" t="s">
+      <c r="D15" s="100" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="98"/>
-      <c r="F15" s="99"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="102"/>
       <c r="G15" s="53" t="s">
         <v>43</v>
       </c>
@@ -3286,16 +3306,16 @@
     </row>
     <row r="16" spans="1:14" ht="100.8">
       <c r="A16" s="10"/>
-      <c r="B16" s="101"/>
+      <c r="B16" s="104"/>
       <c r="C16" s="53" t="str">
         <f>master!C5</f>
         <v>２．クラウドの市場価値向上</v>
       </c>
-      <c r="D16" s="97" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="98"/>
-      <c r="F16" s="99"/>
+      <c r="D16" s="100" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="101"/>
+      <c r="F16" s="102"/>
       <c r="G16" s="53" t="s">
         <v>45</v>
       </c>
@@ -3313,16 +3333,16 @@
     </row>
     <row r="17" spans="1:14" ht="138.6">
       <c r="A17" s="11"/>
-      <c r="B17" s="101"/>
+      <c r="B17" s="104"/>
       <c r="C17" s="53" t="str">
         <f>master!C6</f>
         <v>３．クラウドとは？</v>
       </c>
-      <c r="D17" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="98"/>
-      <c r="F17" s="99"/>
+      <c r="D17" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="101"/>
+      <c r="F17" s="102"/>
       <c r="G17" s="53" t="s">
         <v>38</v>
       </c>
@@ -3338,20 +3358,20 @@
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="88.2">
+    <row r="18" spans="1:14" ht="100.8">
       <c r="A18" s="11"/>
-      <c r="B18" s="101"/>
+      <c r="B18" s="104"/>
       <c r="C18" s="53" t="str">
         <f>master!C7</f>
         <v>４．オンプレミスとのコスト比較</v>
       </c>
-      <c r="D18" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="98"/>
-      <c r="F18" s="99"/>
+      <c r="D18" s="100" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="101"/>
+      <c r="F18" s="102"/>
       <c r="G18" s="53" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="51" t="s">
@@ -3367,16 +3387,16 @@
     </row>
     <row r="19" spans="1:14" ht="201.6">
       <c r="A19" s="11"/>
-      <c r="B19" s="101"/>
+      <c r="B19" s="104"/>
       <c r="C19" s="53" t="str">
         <f>master!C8</f>
         <v>５．クラウドの特徴</v>
       </c>
-      <c r="D19" s="97" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" s="98"/>
-      <c r="F19" s="99"/>
+      <c r="D19" s="100" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="101"/>
+      <c r="F19" s="102"/>
       <c r="G19" s="53" t="s">
         <v>50</v>
       </c>
@@ -3394,16 +3414,16 @@
     </row>
     <row r="20" spans="1:14" ht="113.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="101"/>
+      <c r="B20" s="104"/>
       <c r="C20" s="53" t="str">
         <f>master!C9</f>
         <v>６．クラウドの特徴2</v>
       </c>
-      <c r="D20" s="97" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="98"/>
-      <c r="F20" s="99"/>
+      <c r="D20" s="100" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="101"/>
+      <c r="F20" s="102"/>
       <c r="G20" s="53" t="s">
         <v>42</v>
       </c>
@@ -3421,16 +3441,16 @@
     </row>
     <row r="21" spans="1:14" ht="151.19999999999999">
       <c r="A21" s="11"/>
-      <c r="B21" s="101"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="53" t="str">
         <f>master!C10</f>
         <v>７．アベイラビリティゾーンとリージョン</v>
       </c>
-      <c r="D21" s="97" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="98"/>
-      <c r="F21" s="99"/>
+      <c r="D21" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="101"/>
+      <c r="F21" s="102"/>
       <c r="G21" s="53" t="s">
         <v>49</v>
       </c>
@@ -3448,16 +3468,16 @@
     </row>
     <row r="22" spans="1:14" ht="100.8">
       <c r="A22" s="11"/>
-      <c r="B22" s="101"/>
+      <c r="B22" s="104"/>
       <c r="C22" s="53" t="str">
         <f>master!C11</f>
         <v>８．クラウドにおける責任共有モデル</v>
       </c>
-      <c r="D22" s="97" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="98"/>
-      <c r="F22" s="99"/>
+      <c r="D22" s="100" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="101"/>
+      <c r="F22" s="102"/>
       <c r="G22" s="53" t="s">
         <v>45</v>
       </c>
@@ -3475,16 +3495,16 @@
     </row>
     <row r="23" spans="1:14" ht="37.799999999999997">
       <c r="A23" s="11"/>
-      <c r="B23" s="102"/>
+      <c r="B23" s="105"/>
       <c r="C23" s="53" t="str">
         <f>master!C12</f>
         <v>９．NTTデータはデータセンターが得意　【コラム】</v>
       </c>
-      <c r="D23" s="97" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" s="98"/>
-      <c r="F23" s="99"/>
+      <c r="D23" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="101"/>
+      <c r="F23" s="102"/>
       <c r="G23" s="53" t="s">
         <v>39</v>
       </c>
@@ -3502,7 +3522,7 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="100" t="str">
+      <c r="B24" s="103" t="str">
         <f>master!B13</f>
         <v>AWSとは？</v>
       </c>
@@ -3510,11 +3530,11 @@
         <f>master!C13</f>
         <v>10．AWSとは？</v>
       </c>
-      <c r="D24" s="97" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="98"/>
-      <c r="F24" s="99"/>
+      <c r="D24" s="100" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="101"/>
+      <c r="F24" s="102"/>
       <c r="G24" s="53" t="s">
         <v>41</v>
       </c>
@@ -3532,16 +3552,16 @@
     </row>
     <row r="25" spans="1:14" ht="100.8">
       <c r="A25" s="11"/>
-      <c r="B25" s="101"/>
+      <c r="B25" s="104"/>
       <c r="C25" s="53" t="str">
         <f>master!C14</f>
         <v>11．AWSの利用産業</v>
       </c>
-      <c r="D25" s="97" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="98"/>
-      <c r="F25" s="99"/>
+      <c r="D25" s="100" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="101"/>
+      <c r="F25" s="102"/>
       <c r="G25" s="53" t="s">
         <v>45</v>
       </c>
@@ -3559,18 +3579,18 @@
     </row>
     <row r="26" spans="1:14" ht="176.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="101"/>
+      <c r="B26" s="104"/>
       <c r="C26" s="53" t="str">
         <f>master!C15</f>
         <v>12．Web3層アーキテクチャ</v>
       </c>
-      <c r="D26" s="97" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="98"/>
-      <c r="F26" s="99"/>
+      <c r="D26" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="101"/>
+      <c r="F26" s="102"/>
       <c r="G26" s="53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="51" t="s">
@@ -3586,16 +3606,16 @@
     </row>
     <row r="27" spans="1:14" ht="201.6">
       <c r="A27" s="11"/>
-      <c r="B27" s="101"/>
+      <c r="B27" s="104"/>
       <c r="C27" s="53" t="str">
         <f>master!C16</f>
         <v>13．AWSの基本アーキテクチャ</v>
       </c>
-      <c r="D27" s="97" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" s="98"/>
-      <c r="F27" s="99"/>
+      <c r="D27" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="101"/>
+      <c r="F27" s="102"/>
       <c r="G27" s="53" t="s">
         <v>50</v>
       </c>
@@ -3611,20 +3631,20 @@
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="100.8">
+    <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="101"/>
+      <c r="B28" s="104"/>
       <c r="C28" s="53" t="str">
         <f>master!C17</f>
         <v>14．Amazon VPC（Virtual Private Cloud）</v>
       </c>
-      <c r="D28" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" s="98"/>
-      <c r="F28" s="99"/>
+      <c r="D28" s="100" t="s">
+        <v>164</v>
+      </c>
+      <c r="E28" s="101"/>
+      <c r="F28" s="102"/>
       <c r="G28" s="53" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="51" t="s">
@@ -3640,16 +3660,16 @@
     </row>
     <row r="29" spans="1:14" ht="138.6">
       <c r="A29" s="11"/>
-      <c r="B29" s="101"/>
+      <c r="B29" s="104"/>
       <c r="C29" s="53" t="str">
         <f>master!C18</f>
         <v>15．Amazon EC2（Elastic Compute Cloud）</v>
       </c>
-      <c r="D29" s="97" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="98"/>
-      <c r="F29" s="99"/>
+      <c r="D29" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="101"/>
+      <c r="F29" s="102"/>
       <c r="G29" s="53" t="s">
         <v>38</v>
       </c>
@@ -3667,16 +3687,16 @@
     </row>
     <row r="30" spans="1:14" ht="189">
       <c r="A30" s="11"/>
-      <c r="B30" s="101"/>
+      <c r="B30" s="104"/>
       <c r="C30" s="53" t="str">
         <f>master!C19</f>
         <v>16．Amazon RDS（Relational Database Service）</v>
       </c>
-      <c r="D30" s="97" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" s="98"/>
-      <c r="F30" s="99"/>
+      <c r="D30" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="101"/>
+      <c r="F30" s="102"/>
       <c r="G30" s="53" t="s">
         <v>52</v>
       </c>
@@ -3694,16 +3714,16 @@
     </row>
     <row r="31" spans="1:14" ht="201.6">
       <c r="A31" s="11"/>
-      <c r="B31" s="101"/>
+      <c r="B31" s="104"/>
       <c r="C31" s="53" t="str">
         <f>master!C20</f>
         <v>17．マネージドサービスとは？</v>
       </c>
-      <c r="D31" s="97" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" s="98"/>
-      <c r="F31" s="99"/>
+      <c r="D31" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="101"/>
+      <c r="F31" s="102"/>
       <c r="G31" s="53" t="s">
         <v>50</v>
       </c>
@@ -3721,18 +3741,18 @@
     </row>
     <row r="32" spans="1:14" ht="176.4">
       <c r="A32" s="11"/>
-      <c r="B32" s="101"/>
+      <c r="B32" s="104"/>
       <c r="C32" s="53" t="str">
         <f>master!C21</f>
         <v>18．ELB（Elastic Load Balancing）</v>
       </c>
-      <c r="D32" s="97" t="s">
-        <v>125</v>
-      </c>
-      <c r="E32" s="98"/>
-      <c r="F32" s="99"/>
+      <c r="D32" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="101"/>
+      <c r="F32" s="102"/>
       <c r="G32" s="53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="51" t="s">
@@ -3748,18 +3768,18 @@
     </row>
     <row r="33" spans="1:14" ht="214.2">
       <c r="A33" s="11"/>
-      <c r="B33" s="101"/>
+      <c r="B33" s="104"/>
       <c r="C33" s="53" t="str">
         <f>master!C22</f>
         <v>19．Amazon S3（Simple Storage Service）</v>
       </c>
-      <c r="D33" s="97" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33" s="98"/>
-      <c r="F33" s="99"/>
+      <c r="D33" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="101"/>
+      <c r="F33" s="102"/>
       <c r="G33" s="53" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="51" t="s">
@@ -3775,18 +3795,18 @@
     </row>
     <row r="34" spans="1:14" ht="176.4">
       <c r="A34" s="11"/>
-      <c r="B34" s="101"/>
+      <c r="B34" s="104"/>
       <c r="C34" s="53" t="str">
         <f>master!C23</f>
         <v>20．Amazon CloudWatch</v>
       </c>
-      <c r="D34" s="97" t="s">
-        <v>132</v>
-      </c>
-      <c r="E34" s="98"/>
-      <c r="F34" s="99"/>
+      <c r="D34" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="101"/>
+      <c r="F34" s="102"/>
       <c r="G34" s="53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="51" t="s">
@@ -3802,18 +3822,18 @@
     </row>
     <row r="35" spans="1:14" ht="239.4">
       <c r="A35" s="11"/>
-      <c r="B35" s="101"/>
+      <c r="B35" s="104"/>
       <c r="C35" s="53" t="str">
         <f>master!C24</f>
         <v>21．コンピューティングサービス</v>
       </c>
-      <c r="D35" s="97" t="s">
-        <v>135</v>
-      </c>
-      <c r="E35" s="98"/>
-      <c r="F35" s="99"/>
+      <c r="D35" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="101"/>
+      <c r="F35" s="102"/>
       <c r="G35" s="53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="51" t="s">
@@ -3829,18 +3849,18 @@
     </row>
     <row r="36" spans="1:14" ht="277.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="101"/>
+      <c r="B36" s="104"/>
       <c r="C36" s="53" t="str">
         <f>master!C25</f>
         <v>22．コンテナとは？</v>
       </c>
-      <c r="D36" s="97" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36" s="98"/>
-      <c r="F36" s="99"/>
+      <c r="D36" s="100" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="101"/>
+      <c r="F36" s="102"/>
       <c r="G36" s="53" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="51" t="s">
@@ -3856,18 +3876,18 @@
     </row>
     <row r="37" spans="1:14" ht="327.60000000000002">
       <c r="A37" s="11"/>
-      <c r="B37" s="101"/>
+      <c r="B37" s="104"/>
       <c r="C37" s="53" t="str">
         <f>master!C26</f>
         <v>23．Amazon ECS (Elastic Container Service)</v>
       </c>
-      <c r="D37" s="97" t="s">
-        <v>138</v>
-      </c>
-      <c r="E37" s="98"/>
-      <c r="F37" s="99"/>
+      <c r="D37" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="101"/>
+      <c r="F37" s="102"/>
       <c r="G37" s="53" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="51" t="s">
@@ -3883,18 +3903,18 @@
     </row>
     <row r="38" spans="1:14" ht="126">
       <c r="A38" s="11"/>
-      <c r="B38" s="101"/>
+      <c r="B38" s="104"/>
       <c r="C38" s="53" t="str">
         <f>master!C27</f>
         <v>24．AWS Lambda</v>
       </c>
-      <c r="D38" s="97" t="s">
-        <v>140</v>
-      </c>
-      <c r="E38" s="98"/>
-      <c r="F38" s="99"/>
+      <c r="D38" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="101"/>
+      <c r="F38" s="102"/>
       <c r="G38" s="53" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="51" t="s">
@@ -3910,14 +3930,14 @@
     </row>
     <row r="39" spans="1:14" ht="25.2">
       <c r="A39" s="11"/>
-      <c r="B39" s="102"/>
+      <c r="B39" s="105"/>
       <c r="C39" s="53" t="str">
         <f>master!C28</f>
         <v>25．その他の周辺サービス</v>
       </c>
-      <c r="D39" s="97"/>
-      <c r="E39" s="98"/>
-      <c r="F39" s="99"/>
+      <c r="D39" s="100"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="102"/>
       <c r="G39" s="53" t="s">
         <v>44</v>
       </c>
@@ -3935,7 +3955,7 @@
     </row>
     <row r="40" spans="1:14" ht="252">
       <c r="A40" s="11"/>
-      <c r="B40" s="100" t="str">
+      <c r="B40" s="103" t="str">
         <f>master!B29</f>
         <v>CDKとは？</v>
       </c>
@@ -3943,13 +3963,13 @@
         <f>master!C29</f>
         <v>26．AWS、Azure、Google Cloudの違い　【コラム】</v>
       </c>
-      <c r="D40" s="97" t="s">
-        <v>142</v>
-      </c>
-      <c r="E40" s="98"/>
-      <c r="F40" s="99"/>
+      <c r="D40" s="100" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="101"/>
+      <c r="F40" s="102"/>
       <c r="G40" s="53" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="51" t="s">
@@ -3965,16 +3985,16 @@
     </row>
     <row r="41" spans="1:14" ht="189">
       <c r="A41" s="11"/>
-      <c r="B41" s="101"/>
+      <c r="B41" s="104"/>
       <c r="C41" s="53" t="str">
         <f>master!C30</f>
         <v>27．Infrastructure as Code (IaC) とは？</v>
       </c>
-      <c r="D41" s="97" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="98"/>
-      <c r="F41" s="99"/>
+      <c r="D41" s="100" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="101"/>
+      <c r="F41" s="102"/>
       <c r="G41" s="53" t="s">
         <v>52</v>
       </c>
@@ -3992,18 +4012,18 @@
     </row>
     <row r="42" spans="1:14" ht="226.8">
       <c r="A42" s="11"/>
-      <c r="B42" s="101"/>
+      <c r="B42" s="104"/>
       <c r="C42" s="53" t="str">
         <f>master!C31</f>
         <v>28．IaCのメリット</v>
       </c>
-      <c r="D42" s="97" t="s">
-        <v>144</v>
-      </c>
-      <c r="E42" s="98"/>
-      <c r="F42" s="99"/>
+      <c r="D42" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="101"/>
+      <c r="F42" s="102"/>
       <c r="G42" s="53" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="51" t="s">
@@ -4019,18 +4039,18 @@
     </row>
     <row r="43" spans="1:14" ht="239.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="101"/>
+      <c r="B43" s="104"/>
       <c r="C43" s="53" t="str">
         <f>master!C32</f>
         <v>29．IaCを実現するためのAWSサービス</v>
       </c>
-      <c r="D43" s="97" t="s">
-        <v>145</v>
-      </c>
-      <c r="E43" s="98"/>
-      <c r="F43" s="99"/>
+      <c r="D43" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="101"/>
+      <c r="F43" s="102"/>
       <c r="G43" s="53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="51" t="s">
@@ -4046,18 +4066,18 @@
     </row>
     <row r="44" spans="1:14" ht="239.4">
       <c r="A44" s="11"/>
-      <c r="B44" s="101"/>
+      <c r="B44" s="104"/>
       <c r="C44" s="53" t="str">
         <f>master!C33</f>
         <v>30．AWS CDKのメリット</v>
       </c>
-      <c r="D44" s="97" t="s">
-        <v>146</v>
-      </c>
-      <c r="E44" s="98"/>
-      <c r="F44" s="99"/>
+      <c r="D44" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="101"/>
+      <c r="F44" s="102"/>
       <c r="G44" s="53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="51" t="s">
@@ -4073,18 +4093,18 @@
     </row>
     <row r="45" spans="1:14" ht="264.60000000000002">
       <c r="A45" s="11"/>
-      <c r="B45" s="101"/>
+      <c r="B45" s="104"/>
       <c r="C45" s="53" t="str">
         <f>master!C34</f>
         <v>31．AWS CDKの仕組み</v>
       </c>
-      <c r="D45" s="97" t="s">
-        <v>147</v>
-      </c>
-      <c r="E45" s="98"/>
-      <c r="F45" s="99"/>
+      <c r="D45" s="100" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" s="101"/>
+      <c r="F45" s="102"/>
       <c r="G45" s="53" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="51" t="s">
@@ -4098,20 +4118,20 @@
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="113.4">
+    <row r="46" spans="1:14" ht="100.8">
       <c r="A46" s="11"/>
-      <c r="B46" s="101"/>
+      <c r="B46" s="104"/>
       <c r="C46" s="53" t="str">
         <f>master!C35</f>
         <v>32．AWS CloudFormationとの違い</v>
       </c>
-      <c r="D46" s="97" t="s">
-        <v>148</v>
-      </c>
-      <c r="E46" s="98"/>
-      <c r="F46" s="99"/>
+      <c r="D46" s="100" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" s="101"/>
+      <c r="F46" s="102"/>
       <c r="G46" s="53" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="51" t="s">
@@ -4127,16 +4147,16 @@
     </row>
     <row r="47" spans="1:14" ht="163.80000000000001">
       <c r="A47" s="11"/>
-      <c r="B47" s="101"/>
+      <c r="B47" s="104"/>
       <c r="C47" s="53" t="str">
         <f>master!C36</f>
         <v>33．クラウド移⾏時の7つの⽅式</v>
       </c>
-      <c r="D47" s="97" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" s="98"/>
-      <c r="F47" s="99"/>
+      <c r="D47" s="100" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="101"/>
+      <c r="F47" s="102"/>
       <c r="G47" s="53" t="s">
         <v>51</v>
       </c>
@@ -4154,16 +4174,16 @@
     </row>
     <row r="48" spans="1:14" ht="138.6">
       <c r="A48" s="11"/>
-      <c r="B48" s="101"/>
+      <c r="B48" s="104"/>
       <c r="C48" s="53" t="str">
         <f>master!C37</f>
         <v>34．移行イメージ</v>
       </c>
-      <c r="D48" s="97" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" s="98"/>
-      <c r="F48" s="99"/>
+      <c r="D48" s="100" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" s="101"/>
+      <c r="F48" s="102"/>
       <c r="G48" s="53" t="s">
         <v>38</v>
       </c>
@@ -4181,16 +4201,16 @@
     </row>
     <row r="49" spans="1:14" ht="138.6">
       <c r="A49" s="11"/>
-      <c r="B49" s="102"/>
+      <c r="B49" s="105"/>
       <c r="C49" s="53" t="str">
         <f>master!C38</f>
         <v>35．ReplatformとRefactorの比較</v>
       </c>
-      <c r="D49" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49" s="98"/>
-      <c r="F49" s="99"/>
+      <c r="D49" s="100" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="101"/>
+      <c r="F49" s="102"/>
       <c r="G49" s="53" t="s">
         <v>38</v>
       </c>
@@ -4208,7 +4228,7 @@
     </row>
     <row r="50" spans="1:14" ht="50.4">
       <c r="A50" s="11"/>
-      <c r="B50" s="100" t="str">
+      <c r="B50" s="103" t="str">
         <f>master!B39</f>
         <v>ガバクラとは？</v>
       </c>
@@ -4216,11 +4236,11 @@
         <f>master!C39</f>
         <v>36．ガバメントクラウドとは？</v>
       </c>
-      <c r="D50" s="97" t="s">
-        <v>152</v>
-      </c>
-      <c r="E50" s="98"/>
-      <c r="F50" s="99"/>
+      <c r="D50" s="100" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" s="101"/>
+      <c r="F50" s="102"/>
       <c r="G50" s="53" t="s">
         <v>40</v>
       </c>
@@ -4238,18 +4258,18 @@
     </row>
     <row r="51" spans="1:14" ht="176.4">
       <c r="A51" s="11"/>
-      <c r="B51" s="101"/>
+      <c r="B51" s="104"/>
       <c r="C51" s="53" t="str">
         <f>master!C40</f>
         <v>37．ガバメントクラウド対象</v>
       </c>
-      <c r="D51" s="97" t="s">
-        <v>153</v>
-      </c>
-      <c r="E51" s="98"/>
-      <c r="F51" s="99"/>
+      <c r="D51" s="100" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" s="101"/>
+      <c r="F51" s="102"/>
       <c r="G51" s="53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="51" t="s">
@@ -4265,18 +4285,18 @@
     </row>
     <row r="52" spans="1:14" ht="289.8">
       <c r="A52" s="11"/>
-      <c r="B52" s="101"/>
+      <c r="B52" s="104"/>
       <c r="C52" s="53" t="str">
         <f>master!C41</f>
         <v>38．ガバナンスとセキュリティ</v>
       </c>
-      <c r="D52" s="97" t="s">
-        <v>154</v>
-      </c>
-      <c r="E52" s="98"/>
-      <c r="F52" s="99"/>
+      <c r="D52" s="100" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="101"/>
+      <c r="F52" s="102"/>
       <c r="G52" s="53" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="51" t="s">
@@ -4292,16 +4312,16 @@
     </row>
     <row r="53" spans="1:14" ht="189">
       <c r="A53" s="11"/>
-      <c r="B53" s="101"/>
+      <c r="B53" s="104"/>
       <c r="C53" s="53" t="str">
         <f>master!C42</f>
         <v>39．ガバメントクラウドテンプレート</v>
       </c>
-      <c r="D53" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" s="98"/>
-      <c r="F53" s="99"/>
+      <c r="D53" s="100" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="101"/>
+      <c r="F53" s="102"/>
       <c r="G53" s="53" t="s">
         <v>52</v>
       </c>
@@ -4319,16 +4339,16 @@
     </row>
     <row r="54" spans="1:14" ht="163.80000000000001">
       <c r="A54" s="11"/>
-      <c r="B54" s="101"/>
+      <c r="B54" s="104"/>
       <c r="C54" s="53" t="str">
         <f>master!C43</f>
         <v>40．マネージドサービスの活用</v>
       </c>
-      <c r="D54" s="97" t="s">
-        <v>156</v>
-      </c>
-      <c r="E54" s="98"/>
-      <c r="F54" s="99"/>
+      <c r="D54" s="100" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="101"/>
+      <c r="F54" s="102"/>
       <c r="G54" s="53" t="s">
         <v>51</v>
       </c>
@@ -4346,18 +4366,18 @@
     </row>
     <row r="55" spans="1:14" ht="239.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="101"/>
+      <c r="B55" s="104"/>
       <c r="C55" s="53" t="str">
         <f>master!C44</f>
         <v>41．リアーキテクチャとは？</v>
       </c>
-      <c r="D55" s="97" t="s">
-        <v>157</v>
-      </c>
-      <c r="E55" s="98"/>
-      <c r="F55" s="99"/>
+      <c r="D55" s="100" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" s="101"/>
+      <c r="F55" s="102"/>
       <c r="G55" s="53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="51" t="s">
@@ -4373,18 +4393,18 @@
     </row>
     <row r="56" spans="1:14" ht="176.4">
       <c r="A56" s="11"/>
-      <c r="B56" s="101"/>
+      <c r="B56" s="104"/>
       <c r="C56" s="53" t="str">
         <f>master!C45</f>
         <v>42．リアーキテクチャの重要性</v>
       </c>
-      <c r="D56" s="97" t="s">
-        <v>158</v>
-      </c>
-      <c r="E56" s="98"/>
-      <c r="F56" s="99"/>
+      <c r="D56" s="100" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" s="101"/>
+      <c r="F56" s="102"/>
       <c r="G56" s="53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="51" t="s">
@@ -4400,18 +4420,18 @@
     </row>
     <row r="57" spans="1:14" ht="239.4">
       <c r="A57" s="11"/>
-      <c r="B57" s="101"/>
+      <c r="B57" s="104"/>
       <c r="C57" s="53" t="str">
         <f>master!C46</f>
         <v>43．リアーキテクチャの実施プロセス</v>
       </c>
-      <c r="D57" s="97" t="s">
-        <v>159</v>
-      </c>
-      <c r="E57" s="98"/>
-      <c r="F57" s="99"/>
+      <c r="D57" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="E57" s="101"/>
+      <c r="F57" s="102"/>
       <c r="G57" s="53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="51" t="s">
@@ -4427,18 +4447,18 @@
     </row>
     <row r="58" spans="1:14" ht="302.39999999999998">
       <c r="A58" s="11"/>
-      <c r="B58" s="101"/>
+      <c r="B58" s="104"/>
       <c r="C58" s="53" t="str">
         <f>master!C47</f>
         <v>44．リアーキテクチャの手法</v>
       </c>
-      <c r="D58" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="E58" s="98"/>
-      <c r="F58" s="99"/>
+      <c r="D58" s="100" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" s="101"/>
+      <c r="F58" s="102"/>
       <c r="G58" s="53" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="51" t="s">
@@ -4454,16 +4474,16 @@
     </row>
     <row r="59" spans="1:14" ht="25.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="101"/>
+      <c r="B59" s="104"/>
       <c r="C59" s="53" t="str">
         <f>master!C48</f>
         <v>45．本講義のまとめ</v>
       </c>
-      <c r="D59" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="E59" s="98"/>
-      <c r="F59" s="99"/>
+      <c r="D59" s="100" t="s">
+        <v>153</v>
+      </c>
+      <c r="E59" s="101"/>
+      <c r="F59" s="102"/>
       <c r="G59" s="53" t="s">
         <v>44</v>
       </c>
@@ -4481,57 +4501,57 @@
     </row>
     <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="101"/>
+      <c r="B60" s="104"/>
       <c r="C60" s="53" t="str">
         <f>master!C49</f>
         <v>46．AWS CDKの講師デモ</v>
       </c>
-      <c r="D60" s="97" t="s">
-        <v>160</v>
-      </c>
-      <c r="E60" s="98"/>
-      <c r="F60" s="99"/>
+      <c r="D60" s="100" t="s">
+        <v>150</v>
+      </c>
+      <c r="E60" s="101"/>
+      <c r="F60" s="102"/>
       <c r="G60" s="53" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="H60" s="12"/>
       <c r="I60" s="51" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="J60" s="49">
         <v>1.3888888888888888E-2</v>
       </c>
       <c r="K60" s="46" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:14" ht="75.599999999999994">
+    <row r="61" spans="1:14" ht="88.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="102"/>
+      <c r="B61" s="105"/>
       <c r="C61" s="53" t="str">
         <f>master!C50</f>
         <v>47．AWS 豆知識　【コラム】</v>
       </c>
-      <c r="D61" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="E61" s="98"/>
-      <c r="F61" s="99"/>
+      <c r="D61" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="E61" s="101"/>
+      <c r="F61" s="102"/>
       <c r="G61" s="53" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="51" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="J61" s="49">
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K61" s="46" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
@@ -4539,29 +4559,27 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B15:B23"/>
+    <mergeCell ref="B24:B39"/>
+    <mergeCell ref="B40:B49"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
     <mergeCell ref="B50:B61"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="D57:F57"/>
@@ -4578,27 +4596,29 @@
     <mergeCell ref="D58:F58"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B15:B23"/>
-    <mergeCell ref="B24:B39"/>
-    <mergeCell ref="B40:B49"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4631,7 +4651,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="2:3">

--- a/IG/AI Native-AWS_IG.xlsx
+++ b/IG/AI Native-AWS_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E88966D-4F71-411A-B4F1-DD0C3192B991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAF8102-2C2D-4E90-97FB-E3B4CD19EC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -33,7 +33,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{C2A8E670-0465-455D-8C47-3C85B4C1691E}">
       <text>
         <r>
           <rPr>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="167">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -310,19 +310,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>研修ファイルサーバの保存先</t>
-    <rPh sb="0" eb="2">
-      <t>ケンシュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>実施上のの注意点</t>
@@ -1303,7 +1290,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1380,13 +1367,6 @@
       <b/>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1707,7 +1687,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1747,13 +1727,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1771,25 +1751,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1801,212 +1772,203 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2025,6 +1987,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2398,15 +2375,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="81" t="str">
+      <c r="B2" s="78" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-AWS_IG」</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -2419,10 +2396,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="83"/>
+      <c r="C4" s="80"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -2430,34 +2407,34 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="85"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="86"/>
+      <c r="C7" s="83"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A10" s="40">
+      <c r="A10" s="37">
         <v>0.39583333333333331</v>
       </c>
       <c r="B10" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -2465,327 +2442,327 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="42"/>
-      <c r="B11" s="65">
+      <c r="A11" s="39"/>
+      <c r="B11" s="62">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="68" t="str">
+      <c r="C11" s="65" t="str">
         <f>master!B4</f>
         <v>クラウドとは？</v>
       </c>
       <c r="G11" s="14"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="40">
+      <c r="A12" s="37">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="66"/>
       <c r="G12" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="41"/>
-      <c r="B13" s="65">
+      <c r="A13" s="38"/>
+      <c r="B13" s="62">
         <v>0.42708333333333331</v>
       </c>
-      <c r="C13" s="68" t="str">
+      <c r="C13" s="65" t="str">
         <f>master!B13</f>
         <v>AWSとは？</v>
       </c>
-      <c r="F13" s="26"/>
+      <c r="F13" s="23"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="41"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="69"/>
-      <c r="F14" s="80"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="66"/>
+      <c r="F14" s="77"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="42"/>
-      <c r="B15" s="54" t="s">
+      <c r="A15" s="39"/>
+      <c r="B15" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="F15" s="80"/>
+      <c r="C15" s="66"/>
+      <c r="F15" s="77"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="40">
+      <c r="A16" s="37">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="70"/>
-      <c r="F16" s="80"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="67"/>
+      <c r="F16" s="77"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="41"/>
-      <c r="B17" s="43">
+      <c r="A17" s="38"/>
+      <c r="B17" s="40">
         <v>0.46875</v>
       </c>
-      <c r="C17" s="68" t="str">
+      <c r="C17" s="65" t="str">
         <f>master!B29</f>
         <v>CDKとは？</v>
       </c>
-      <c r="F17" s="80"/>
+      <c r="F17" s="77"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="41"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="69"/>
-      <c r="F18" s="80"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="66"/>
+      <c r="F18" s="77"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="42"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="70"/>
-      <c r="F19" s="80"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="67"/>
+      <c r="F19" s="77"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="64">
+      <c r="A20" s="61">
         <v>0.5</v>
       </c>
-      <c r="B20" s="64">
+      <c r="B20" s="61">
         <v>0.5</v>
       </c>
-      <c r="C20" s="68" t="str">
+      <c r="C20" s="65" t="str">
         <f>master!B39</f>
         <v>ガバクラとは？</v>
       </c>
-      <c r="F20" s="80"/>
+      <c r="F20" s="77"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="59"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="70"/>
-      <c r="F21" s="80"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="67"/>
+      <c r="F21" s="77"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="25"/>
+      <c r="F22" s="22"/>
       <c r="G22" s="10"/>
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="42"/>
-      <c r="B23" s="41" t="s">
+      <c r="A23" s="39"/>
+      <c r="B23" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="73"/>
-      <c r="F23" s="25"/>
+      <c r="C23" s="70"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="10"/>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="40">
+      <c r="A24" s="37">
         <v>0.54166666666666663</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="73"/>
-      <c r="F24" s="25"/>
+      <c r="C24" s="70"/>
+      <c r="F24" s="22"/>
       <c r="G24" s="10"/>
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="41"/>
-      <c r="B25" s="42" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="74"/>
-      <c r="F25" s="25"/>
+      <c r="C25" s="71"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="10"/>
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="41"/>
-      <c r="B26" s="43">
+      <c r="A26" s="38"/>
+      <c r="B26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="77"/>
-      <c r="F26" s="80"/>
+      <c r="C26" s="74"/>
+      <c r="F26" s="77"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="42"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="78"/>
-      <c r="F27" s="80"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="75"/>
+      <c r="F27" s="77"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="40">
+      <c r="A28" s="37">
         <v>0.58333333333333337</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="78"/>
-      <c r="F28" s="80"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="75"/>
+      <c r="F28" s="77"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="41"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="80"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="77"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="41"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="80"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="77"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="42"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="58"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="80"/>
+      <c r="F31" s="77"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="64">
+      <c r="A32" s="61">
         <v>0.625</v>
       </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="58"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="80"/>
+      <c r="F32" s="77"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="59"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="80"/>
+      <c r="A33" s="56"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="77"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="59"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="80"/>
+      <c r="A34" s="56"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="77"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="42"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="80"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="77"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="40">
+      <c r="A36" s="37">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="58"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="55"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="80"/>
+      <c r="F36" s="77"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="41"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="58"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="80"/>
+      <c r="F37" s="77"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="41"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="58"/>
+      <c r="A38" s="38"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="55"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="80"/>
+      <c r="F38" s="77"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="41"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="58"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="55"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="80"/>
+      <c r="F39" s="77"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="43">
+      <c r="A40" s="40">
         <v>0.70833333333333337</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="80"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="77"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="41"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="80"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="77"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="45"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="80"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="77"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A43" s="44"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="79"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="25"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.6" thickBot="1">
       <c r="A44" s="6"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="21"/>
       <c r="H44" s="6"/>
     </row>
   </sheetData>
@@ -2809,7 +2786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L13"/>
+  <dimension ref="A2:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -2819,25 +2796,25 @@
     <col min="5" max="5" width="16.33203125" style="10" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="30" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" style="27" customWidth="1"/>
     <col min="9" max="10" width="6.6640625" style="10" customWidth="1"/>
     <col min="11" max="11" width="38.44140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="4.6640625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" s="34" customFormat="1" ht="36.75" customHeight="1">
+    <row r="2" spans="1:12" s="31" customFormat="1" ht="36.75" customHeight="1">
       <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:12">
@@ -2846,36 +2823,36 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="29"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="19"/>
       <c r="J3" s="19"/>
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="92"/>
+      <c r="C4" s="89"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="29"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -2884,132 +2861,126 @@
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="94" t="s">
+      <c r="C7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="94"/>
-      <c r="F7" s="36" t="s">
+      <c r="E7" s="91"/>
+      <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="48" t="s">
+      <c r="C8" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="39" t="s">
+      <c r="E8" s="44"/>
+      <c r="F8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="36" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="24"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="G9" s="10"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+    <row r="10" spans="1:12">
+      <c r="A10" s="10"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="88" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="95" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="87" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="87"/>
-      <c r="K11" s="87" t="s">
-        <v>32</v>
-      </c>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="85"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="63">
       <c r="A12" s="10"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="87"/>
       <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="88"/>
+      <c r="G12" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="60">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K12" s="20"/>
       <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:12" ht="63">
-      <c r="A13" s="10"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="90"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="62" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="63">
-        <v>1.0416666666666666E-2</v>
-      </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:J10"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3022,7 +2993,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
+          <xm:sqref>H12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3082,12 +3053,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="92"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="92"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3098,32 +3069,32 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="33"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="33"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="10"/>
@@ -3135,23 +3106,23 @@
       <c r="M7" s="10"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36" t="s">
+      <c r="D8" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="91"/>
+      <c r="F8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="50"/>
+      <c r="I8" s="47"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -3159,20 +3130,20 @@
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="B9" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="39" t="s">
+      <c r="B9" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39" t="s">
+      <c r="E9" s="104"/>
+      <c r="F9" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="36" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="6"/>
@@ -3181,20 +3152,20 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="B10" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="39" t="s">
+      <c r="B10" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39" t="s">
+      <c r="E10" s="104"/>
+      <c r="F10" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="36" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="6"/>
@@ -3203,20 +3174,20 @@
       <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="B11" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="39" t="s">
+      <c r="B11" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39" t="s">
+      <c r="E11" s="104"/>
+      <c r="F11" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="36" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="6"/>
@@ -3226,29 +3197,29 @@
     </row>
     <row r="13" spans="1:14" ht="24" customHeight="1">
       <c r="A13" s="10"/>
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88" t="s">
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="87" t="s">
+      <c r="H13" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="97" t="s">
+      <c r="I13" s="100" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="101"/>
+      <c r="K13" s="84" t="s">
         <v>33</v>
-      </c>
-      <c r="J13" s="98"/>
-      <c r="K13" s="87" t="s">
-        <v>34</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -3256,1273 +3227,1273 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="10"/>
-      <c r="B14" s="88"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="31" t="s">
+      <c r="B14" s="85"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K14" s="88"/>
+      <c r="K14" s="85"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="88.2">
       <c r="A15" s="10"/>
-      <c r="B15" s="103" t="str">
+      <c r="B15" s="97" t="str">
         <f>master!B4</f>
         <v>クラウドとは？</v>
       </c>
-      <c r="C15" s="53" t="str">
+      <c r="C15" s="50" t="str">
         <f>master!C4</f>
         <v>１．IT業界の歴史</v>
       </c>
-      <c r="D15" s="100" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="101"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="53" t="s">
-        <v>43</v>
+      <c r="D15" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="95"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="50" t="s">
+        <v>42</v>
       </c>
       <c r="H15" s="12"/>
-      <c r="I15" s="51" t="s">
+      <c r="I15" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="49">
+      <c r="J15" s="46">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K15" s="46"/>
+      <c r="K15" s="43"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="100.8">
       <c r="A16" s="10"/>
-      <c r="B16" s="104"/>
-      <c r="C16" s="53" t="str">
+      <c r="B16" s="98"/>
+      <c r="C16" s="50" t="str">
         <f>master!C5</f>
         <v>２．クラウドの市場価値向上</v>
       </c>
-      <c r="D16" s="100" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="101"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="53" t="s">
-        <v>45</v>
+      <c r="D16" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="95"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="50" t="s">
+        <v>44</v>
       </c>
       <c r="H16" s="12"/>
-      <c r="I16" s="51" t="s">
+      <c r="I16" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K16" s="46"/>
+      <c r="K16" s="43"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="138.6">
       <c r="A17" s="11"/>
-      <c r="B17" s="104"/>
-      <c r="C17" s="53" t="str">
+      <c r="B17" s="98"/>
+      <c r="C17" s="50" t="str">
         <f>master!C6</f>
         <v>３．クラウドとは？</v>
       </c>
-      <c r="D17" s="100" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="101"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="53" t="s">
-        <v>38</v>
+      <c r="D17" s="94" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="95"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="H17" s="12"/>
-      <c r="I17" s="51" t="s">
+      <c r="I17" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K17" s="46"/>
+      <c r="K17" s="43"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" ht="100.8">
       <c r="A18" s="11"/>
-      <c r="B18" s="104"/>
-      <c r="C18" s="53" t="str">
+      <c r="B18" s="98"/>
+      <c r="C18" s="50" t="str">
         <f>master!C7</f>
         <v>４．オンプレミスとのコスト比較</v>
       </c>
-      <c r="D18" s="100" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" s="101"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="53" t="s">
-        <v>45</v>
+      <c r="D18" s="94" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="95"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="50" t="s">
+        <v>44</v>
       </c>
       <c r="H18" s="12"/>
-      <c r="I18" s="51" t="s">
+      <c r="I18" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="49">
+      <c r="J18" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K18" s="46"/>
+      <c r="K18" s="43"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="1:14" ht="201.6">
       <c r="A19" s="11"/>
-      <c r="B19" s="104"/>
-      <c r="C19" s="53" t="str">
+      <c r="B19" s="98"/>
+      <c r="C19" s="50" t="str">
         <f>master!C8</f>
         <v>５．クラウドの特徴</v>
       </c>
-      <c r="D19" s="100" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="101"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="53" t="s">
-        <v>50</v>
+      <c r="D19" s="94" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="95"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="50" t="s">
+        <v>49</v>
       </c>
       <c r="H19" s="12"/>
-      <c r="I19" s="51" t="s">
+      <c r="I19" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J19" s="49">
+      <c r="J19" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K19" s="46"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="1:14" ht="113.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="104"/>
-      <c r="C20" s="53" t="str">
+      <c r="B20" s="98"/>
+      <c r="C20" s="50" t="str">
         <f>master!C9</f>
         <v>６．クラウドの特徴2</v>
       </c>
-      <c r="D20" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="101"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="53" t="s">
-        <v>42</v>
+      <c r="D20" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="50" t="s">
+        <v>41</v>
       </c>
       <c r="H20" s="12"/>
-      <c r="I20" s="51" t="s">
+      <c r="I20" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="49">
+      <c r="J20" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K20" s="46"/>
+      <c r="K20" s="43"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
     <row r="21" spans="1:14" ht="151.19999999999999">
       <c r="A21" s="11"/>
-      <c r="B21" s="104"/>
-      <c r="C21" s="53" t="str">
+      <c r="B21" s="98"/>
+      <c r="C21" s="50" t="str">
         <f>master!C10</f>
         <v>７．アベイラビリティゾーンとリージョン</v>
       </c>
-      <c r="D21" s="100" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" s="101"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="53" t="s">
-        <v>49</v>
+      <c r="D21" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="95"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="50" t="s">
+        <v>48</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="51" t="s">
+      <c r="I21" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J21" s="49">
+      <c r="J21" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K21" s="46"/>
+      <c r="K21" s="43"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" ht="100.8">
       <c r="A22" s="11"/>
-      <c r="B22" s="104"/>
-      <c r="C22" s="53" t="str">
+      <c r="B22" s="98"/>
+      <c r="C22" s="50" t="str">
         <f>master!C11</f>
         <v>８．クラウドにおける責任共有モデル</v>
       </c>
-      <c r="D22" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="101"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="53" t="s">
-        <v>45</v>
+      <c r="D22" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="95"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="50" t="s">
+        <v>44</v>
       </c>
       <c r="H22" s="12"/>
-      <c r="I22" s="51" t="s">
+      <c r="I22" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J22" s="49">
+      <c r="J22" s="46">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K22" s="46"/>
+      <c r="K22" s="43"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" ht="37.799999999999997">
       <c r="A23" s="11"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="53" t="str">
+      <c r="B23" s="99"/>
+      <c r="C23" s="50" t="str">
         <f>master!C12</f>
         <v>９．NTTデータはデータセンターが得意　【コラム】</v>
       </c>
-      <c r="D23" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" s="101"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="53" t="s">
-        <v>39</v>
+      <c r="D23" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="95"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="50" t="s">
+        <v>38</v>
       </c>
       <c r="H23" s="12"/>
-      <c r="I23" s="51" t="s">
+      <c r="I23" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="49">
+      <c r="J23" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K23" s="46"/>
+      <c r="K23" s="43"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="103" t="str">
+      <c r="B24" s="97" t="str">
         <f>master!B13</f>
         <v>AWSとは？</v>
       </c>
-      <c r="C24" s="53" t="str">
+      <c r="C24" s="50" t="str">
         <f>master!C13</f>
         <v>10．AWSとは？</v>
       </c>
-      <c r="D24" s="100" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="101"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="53" t="s">
-        <v>41</v>
+      <c r="D24" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="95"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="50" t="s">
+        <v>40</v>
       </c>
       <c r="H24" s="12"/>
-      <c r="I24" s="51" t="s">
+      <c r="I24" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J24" s="49">
+      <c r="J24" s="46">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K24" s="46"/>
+      <c r="K24" s="43"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" ht="100.8">
       <c r="A25" s="11"/>
-      <c r="B25" s="104"/>
-      <c r="C25" s="53" t="str">
+      <c r="B25" s="98"/>
+      <c r="C25" s="50" t="str">
         <f>master!C14</f>
         <v>11．AWSの利用産業</v>
       </c>
-      <c r="D25" s="100" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="101"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="53" t="s">
-        <v>45</v>
+      <c r="D25" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="95"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="50" t="s">
+        <v>44</v>
       </c>
       <c r="H25" s="12"/>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J25" s="49">
+      <c r="J25" s="46">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K25" s="46"/>
+      <c r="K25" s="43"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="1:14" ht="176.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="53" t="str">
+      <c r="B26" s="98"/>
+      <c r="C26" s="50" t="str">
         <f>master!C15</f>
         <v>12．Web3層アーキテクチャ</v>
       </c>
-      <c r="D26" s="100" t="s">
-        <v>165</v>
-      </c>
-      <c r="E26" s="101"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="53" t="s">
-        <v>116</v>
+      <c r="D26" s="94" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="95"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="50" t="s">
+        <v>115</v>
       </c>
       <c r="H26" s="12"/>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J26" s="49">
+      <c r="J26" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K26" s="46"/>
+      <c r="K26" s="43"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
     <row r="27" spans="1:14" ht="201.6">
       <c r="A27" s="11"/>
-      <c r="B27" s="104"/>
-      <c r="C27" s="53" t="str">
+      <c r="B27" s="98"/>
+      <c r="C27" s="50" t="str">
         <f>master!C16</f>
         <v>13．AWSの基本アーキテクチャ</v>
       </c>
-      <c r="D27" s="100" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="101"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="53" t="s">
-        <v>50</v>
+      <c r="D27" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="95"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="50" t="s">
+        <v>49</v>
       </c>
       <c r="H27" s="12"/>
-      <c r="I27" s="51" t="s">
+      <c r="I27" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="49">
+      <c r="J27" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K27" s="46"/>
+      <c r="K27" s="43"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="104"/>
-      <c r="C28" s="53" t="str">
+      <c r="B28" s="98"/>
+      <c r="C28" s="50" t="str">
         <f>master!C17</f>
         <v>14．Amazon VPC（Virtual Private Cloud）</v>
       </c>
-      <c r="D28" s="100" t="s">
-        <v>164</v>
-      </c>
-      <c r="E28" s="101"/>
-      <c r="F28" s="102"/>
-      <c r="G28" s="53" t="s">
-        <v>42</v>
+      <c r="D28" s="94" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" s="95"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="50" t="s">
+        <v>41</v>
       </c>
       <c r="H28" s="12"/>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J28" s="49">
+      <c r="J28" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K28" s="46"/>
+      <c r="K28" s="43"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
     <row r="29" spans="1:14" ht="138.6">
       <c r="A29" s="11"/>
-      <c r="B29" s="104"/>
-      <c r="C29" s="53" t="str">
+      <c r="B29" s="98"/>
+      <c r="C29" s="50" t="str">
         <f>master!C18</f>
         <v>15．Amazon EC2（Elastic Compute Cloud）</v>
       </c>
-      <c r="D29" s="100" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" s="101"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="53" t="s">
-        <v>38</v>
+      <c r="D29" s="94" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="95"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="H29" s="12"/>
-      <c r="I29" s="51" t="s">
+      <c r="I29" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J29" s="49">
+      <c r="J29" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K29" s="46"/>
+      <c r="K29" s="43"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" ht="189">
       <c r="A30" s="11"/>
-      <c r="B30" s="104"/>
-      <c r="C30" s="53" t="str">
+      <c r="B30" s="98"/>
+      <c r="C30" s="50" t="str">
         <f>master!C19</f>
         <v>16．Amazon RDS（Relational Database Service）</v>
       </c>
-      <c r="D30" s="100" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="101"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="53" t="s">
-        <v>52</v>
+      <c r="D30" s="94" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="95"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="50" t="s">
+        <v>51</v>
       </c>
       <c r="H30" s="12"/>
-      <c r="I30" s="51" t="s">
+      <c r="I30" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J30" s="49">
+      <c r="J30" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K30" s="46"/>
+      <c r="K30" s="43"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" ht="201.6">
       <c r="A31" s="11"/>
-      <c r="B31" s="104"/>
-      <c r="C31" s="53" t="str">
+      <c r="B31" s="98"/>
+      <c r="C31" s="50" t="str">
         <f>master!C20</f>
         <v>17．マネージドサービスとは？</v>
       </c>
-      <c r="D31" s="100" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" s="101"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="53" t="s">
-        <v>50</v>
+      <c r="D31" s="94" t="s">
+        <v>161</v>
+      </c>
+      <c r="E31" s="95"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="50" t="s">
+        <v>49</v>
       </c>
       <c r="H31" s="12"/>
-      <c r="I31" s="51" t="s">
+      <c r="I31" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J31" s="49">
+      <c r="J31" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K31" s="46"/>
+      <c r="K31" s="43"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
     <row r="32" spans="1:14" ht="176.4">
       <c r="A32" s="11"/>
-      <c r="B32" s="104"/>
-      <c r="C32" s="53" t="str">
+      <c r="B32" s="98"/>
+      <c r="C32" s="50" t="str">
         <f>master!C21</f>
         <v>18．ELB（Elastic Load Balancing）</v>
       </c>
-      <c r="D32" s="100" t="s">
-        <v>163</v>
-      </c>
-      <c r="E32" s="101"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="53" t="s">
-        <v>116</v>
+      <c r="D32" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="95"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="50" t="s">
+        <v>115</v>
       </c>
       <c r="H32" s="12"/>
-      <c r="I32" s="51" t="s">
+      <c r="I32" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J32" s="49">
+      <c r="J32" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K32" s="46"/>
+      <c r="K32" s="43"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
     <row r="33" spans="1:14" ht="214.2">
       <c r="A33" s="11"/>
-      <c r="B33" s="104"/>
-      <c r="C33" s="53" t="str">
+      <c r="B33" s="98"/>
+      <c r="C33" s="50" t="str">
         <f>master!C22</f>
         <v>19．Amazon S3（Simple Storage Service）</v>
       </c>
-      <c r="D33" s="100" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" s="101"/>
-      <c r="F33" s="102"/>
-      <c r="G33" s="53" t="s">
+      <c r="D33" s="94" t="s">
         <v>120</v>
       </c>
+      <c r="E33" s="95"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="50" t="s">
+        <v>119</v>
+      </c>
       <c r="H33" s="12"/>
-      <c r="I33" s="51" t="s">
+      <c r="I33" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J33" s="49">
+      <c r="J33" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K33" s="46"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
     <row r="34" spans="1:14" ht="176.4">
       <c r="A34" s="11"/>
-      <c r="B34" s="104"/>
-      <c r="C34" s="53" t="str">
+      <c r="B34" s="98"/>
+      <c r="C34" s="50" t="str">
         <f>master!C23</f>
         <v>20．Amazon CloudWatch</v>
       </c>
-      <c r="D34" s="100" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" s="101"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="53" t="s">
-        <v>116</v>
+      <c r="D34" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" s="95"/>
+      <c r="F34" s="96"/>
+      <c r="G34" s="50" t="s">
+        <v>115</v>
       </c>
       <c r="H34" s="12"/>
-      <c r="I34" s="51" t="s">
+      <c r="I34" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J34" s="49">
+      <c r="J34" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K34" s="46"/>
+      <c r="K34" s="43"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
     <row r="35" spans="1:14" ht="239.4">
       <c r="A35" s="11"/>
-      <c r="B35" s="104"/>
-      <c r="C35" s="53" t="str">
+      <c r="B35" s="98"/>
+      <c r="C35" s="50" t="str">
         <f>master!C24</f>
         <v>21．コンピューティングサービス</v>
       </c>
-      <c r="D35" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" s="101"/>
-      <c r="F35" s="102"/>
-      <c r="G35" s="53" t="s">
-        <v>119</v>
+      <c r="D35" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="95"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="50" t="s">
+        <v>118</v>
       </c>
       <c r="H35" s="12"/>
-      <c r="I35" s="51" t="s">
+      <c r="I35" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J35" s="49">
+      <c r="J35" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K35" s="46"/>
+      <c r="K35" s="43"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
     <row r="36" spans="1:14" ht="277.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="53" t="str">
+      <c r="B36" s="98"/>
+      <c r="C36" s="50" t="str">
         <f>master!C25</f>
         <v>22．コンテナとは？</v>
       </c>
-      <c r="D36" s="100" t="s">
+      <c r="D36" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="95"/>
+      <c r="F36" s="96"/>
+      <c r="G36" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="101"/>
-      <c r="F36" s="102"/>
-      <c r="G36" s="53" t="s">
-        <v>128</v>
-      </c>
       <c r="H36" s="12"/>
-      <c r="I36" s="51" t="s">
+      <c r="I36" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J36" s="49">
+      <c r="J36" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K36" s="46"/>
+      <c r="K36" s="43"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
     <row r="37" spans="1:14" ht="327.60000000000002">
       <c r="A37" s="11"/>
-      <c r="B37" s="104"/>
-      <c r="C37" s="53" t="str">
+      <c r="B37" s="98"/>
+      <c r="C37" s="50" t="str">
         <f>master!C26</f>
         <v>23．Amazon ECS (Elastic Container Service)</v>
       </c>
-      <c r="D37" s="100" t="s">
+      <c r="D37" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="95"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="E37" s="101"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="53" t="s">
-        <v>130</v>
-      </c>
       <c r="H37" s="12"/>
-      <c r="I37" s="51" t="s">
+      <c r="I37" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J37" s="49">
+      <c r="J37" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K37" s="46"/>
+      <c r="K37" s="43"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
     <row r="38" spans="1:14" ht="126">
       <c r="A38" s="11"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="53" t="str">
+      <c r="B38" s="98"/>
+      <c r="C38" s="50" t="str">
         <f>master!C27</f>
         <v>24．AWS Lambda</v>
       </c>
-      <c r="D38" s="100" t="s">
-        <v>131</v>
-      </c>
-      <c r="E38" s="101"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="53" t="s">
-        <v>109</v>
+      <c r="D38" s="94" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="95"/>
+      <c r="F38" s="96"/>
+      <c r="G38" s="50" t="s">
+        <v>108</v>
       </c>
       <c r="H38" s="12"/>
-      <c r="I38" s="51" t="s">
+      <c r="I38" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J38" s="49">
+      <c r="J38" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K38" s="46"/>
+      <c r="K38" s="43"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
     <row r="39" spans="1:14" ht="25.2">
       <c r="A39" s="11"/>
-      <c r="B39" s="105"/>
-      <c r="C39" s="53" t="str">
+      <c r="B39" s="99"/>
+      <c r="C39" s="50" t="str">
         <f>master!C28</f>
         <v>25．その他の周辺サービス</v>
       </c>
-      <c r="D39" s="100"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="53" t="s">
-        <v>44</v>
+      <c r="D39" s="94"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="96"/>
+      <c r="G39" s="50" t="s">
+        <v>43</v>
       </c>
       <c r="H39" s="12"/>
-      <c r="I39" s="51" t="s">
+      <c r="I39" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J39" s="49">
+      <c r="J39" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K39" s="46"/>
+      <c r="K39" s="43"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
     <row r="40" spans="1:14" ht="252">
       <c r="A40" s="11"/>
-      <c r="B40" s="103" t="str">
+      <c r="B40" s="97" t="str">
         <f>master!B29</f>
         <v>CDKとは？</v>
       </c>
-      <c r="C40" s="53" t="str">
+      <c r="C40" s="50" t="str">
         <f>master!C29</f>
         <v>26．AWS、Azure、Google Cloudの違い　【コラム】</v>
       </c>
-      <c r="D40" s="100" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="101"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="53" t="s">
-        <v>117</v>
+      <c r="D40" s="94" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="95"/>
+      <c r="F40" s="96"/>
+      <c r="G40" s="50" t="s">
+        <v>116</v>
       </c>
       <c r="H40" s="12"/>
-      <c r="I40" s="51" t="s">
+      <c r="I40" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J40" s="49">
+      <c r="J40" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K40" s="46"/>
+      <c r="K40" s="43"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
     <row r="41" spans="1:14" ht="189">
       <c r="A41" s="11"/>
-      <c r="B41" s="104"/>
-      <c r="C41" s="53" t="str">
+      <c r="B41" s="98"/>
+      <c r="C41" s="50" t="str">
         <f>master!C30</f>
         <v>27．Infrastructure as Code (IaC) とは？</v>
       </c>
-      <c r="D41" s="100" t="s">
-        <v>133</v>
-      </c>
-      <c r="E41" s="101"/>
-      <c r="F41" s="102"/>
-      <c r="G41" s="53" t="s">
-        <v>52</v>
+      <c r="D41" s="94" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" s="95"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="50" t="s">
+        <v>51</v>
       </c>
       <c r="H41" s="12"/>
-      <c r="I41" s="51" t="s">
+      <c r="I41" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="49">
+      <c r="J41" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K41" s="46"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" ht="226.8">
       <c r="A42" s="11"/>
-      <c r="B42" s="104"/>
-      <c r="C42" s="53" t="str">
+      <c r="B42" s="98"/>
+      <c r="C42" s="50" t="str">
         <f>master!C31</f>
         <v>28．IaCのメリット</v>
       </c>
-      <c r="D42" s="100" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" s="101"/>
-      <c r="F42" s="102"/>
-      <c r="G42" s="53" t="s">
-        <v>132</v>
+      <c r="D42" s="94" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="95"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="50" t="s">
+        <v>131</v>
       </c>
       <c r="H42" s="12"/>
-      <c r="I42" s="51" t="s">
+      <c r="I42" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J42" s="49">
+      <c r="J42" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K42" s="46"/>
+      <c r="K42" s="43"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
     <row r="43" spans="1:14" ht="239.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="104"/>
-      <c r="C43" s="53" t="str">
+      <c r="B43" s="98"/>
+      <c r="C43" s="50" t="str">
         <f>master!C32</f>
         <v>29．IaCを実現するためのAWSサービス</v>
       </c>
-      <c r="D43" s="100" t="s">
-        <v>135</v>
-      </c>
-      <c r="E43" s="101"/>
-      <c r="F43" s="102"/>
-      <c r="G43" s="53" t="s">
-        <v>119</v>
+      <c r="D43" s="94" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="95"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="50" t="s">
+        <v>118</v>
       </c>
       <c r="H43" s="12"/>
-      <c r="I43" s="51" t="s">
+      <c r="I43" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J43" s="49">
+      <c r="J43" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K43" s="46"/>
+      <c r="K43" s="43"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
     <row r="44" spans="1:14" ht="239.4">
       <c r="A44" s="11"/>
-      <c r="B44" s="104"/>
-      <c r="C44" s="53" t="str">
+      <c r="B44" s="98"/>
+      <c r="C44" s="50" t="str">
         <f>master!C33</f>
         <v>30．AWS CDKのメリット</v>
       </c>
-      <c r="D44" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" s="101"/>
-      <c r="F44" s="102"/>
-      <c r="G44" s="53" t="s">
-        <v>119</v>
+      <c r="D44" s="94" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="95"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="50" t="s">
+        <v>118</v>
       </c>
       <c r="H44" s="12"/>
-      <c r="I44" s="51" t="s">
+      <c r="I44" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J44" s="49">
+      <c r="J44" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K44" s="46"/>
+      <c r="K44" s="43"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" ht="264.60000000000002">
       <c r="A45" s="11"/>
-      <c r="B45" s="104"/>
-      <c r="C45" s="53" t="str">
+      <c r="B45" s="98"/>
+      <c r="C45" s="50" t="str">
         <f>master!C34</f>
         <v>31．AWS CDKの仕組み</v>
       </c>
-      <c r="D45" s="100" t="s">
-        <v>137</v>
-      </c>
-      <c r="E45" s="101"/>
-      <c r="F45" s="102"/>
-      <c r="G45" s="53" t="s">
-        <v>124</v>
+      <c r="D45" s="94" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="95"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="50" t="s">
+        <v>123</v>
       </c>
       <c r="H45" s="12"/>
-      <c r="I45" s="51" t="s">
+      <c r="I45" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J45" s="49">
+      <c r="J45" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K45" s="46"/>
+      <c r="K45" s="43"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:14" ht="100.8">
       <c r="A46" s="11"/>
-      <c r="B46" s="104"/>
-      <c r="C46" s="53" t="str">
+      <c r="B46" s="98"/>
+      <c r="C46" s="50" t="str">
         <f>master!C35</f>
         <v>32．AWS CloudFormationとの違い</v>
       </c>
-      <c r="D46" s="100" t="s">
-        <v>138</v>
-      </c>
-      <c r="E46" s="101"/>
-      <c r="F46" s="102"/>
-      <c r="G46" s="53" t="s">
-        <v>45</v>
+      <c r="D46" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="E46" s="95"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="50" t="s">
+        <v>44</v>
       </c>
       <c r="H46" s="12"/>
-      <c r="I46" s="51" t="s">
+      <c r="I46" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J46" s="49">
+      <c r="J46" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K46" s="46"/>
+      <c r="K46" s="43"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
     <row r="47" spans="1:14" ht="163.80000000000001">
       <c r="A47" s="11"/>
-      <c r="B47" s="104"/>
-      <c r="C47" s="53" t="str">
+      <c r="B47" s="98"/>
+      <c r="C47" s="50" t="str">
         <f>master!C36</f>
         <v>33．クラウド移⾏時の7つの⽅式</v>
       </c>
-      <c r="D47" s="100" t="s">
-        <v>139</v>
-      </c>
-      <c r="E47" s="101"/>
-      <c r="F47" s="102"/>
-      <c r="G47" s="53" t="s">
-        <v>51</v>
+      <c r="D47" s="94" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="95"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="50" t="s">
+        <v>50</v>
       </c>
       <c r="H47" s="12"/>
-      <c r="I47" s="51" t="s">
+      <c r="I47" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J47" s="49">
+      <c r="J47" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K47" s="46"/>
+      <c r="K47" s="43"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
     <row r="48" spans="1:14" ht="138.6">
       <c r="A48" s="11"/>
-      <c r="B48" s="104"/>
-      <c r="C48" s="53" t="str">
+      <c r="B48" s="98"/>
+      <c r="C48" s="50" t="str">
         <f>master!C37</f>
         <v>34．移行イメージ</v>
       </c>
-      <c r="D48" s="100" t="s">
-        <v>140</v>
-      </c>
-      <c r="E48" s="101"/>
-      <c r="F48" s="102"/>
-      <c r="G48" s="53" t="s">
-        <v>38</v>
+      <c r="D48" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="95"/>
+      <c r="F48" s="96"/>
+      <c r="G48" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="H48" s="12"/>
-      <c r="I48" s="51" t="s">
+      <c r="I48" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J48" s="49">
+      <c r="J48" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K48" s="46"/>
+      <c r="K48" s="43"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" ht="138.6">
       <c r="A49" s="11"/>
-      <c r="B49" s="105"/>
-      <c r="C49" s="53" t="str">
+      <c r="B49" s="99"/>
+      <c r="C49" s="50" t="str">
         <f>master!C38</f>
         <v>35．ReplatformとRefactorの比較</v>
       </c>
-      <c r="D49" s="100" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" s="101"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="53" t="s">
-        <v>38</v>
+      <c r="D49" s="94" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" s="95"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="H49" s="12"/>
-      <c r="I49" s="51" t="s">
+      <c r="I49" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J49" s="49">
+      <c r="J49" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K49" s="46"/>
+      <c r="K49" s="43"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="50.4">
       <c r="A50" s="11"/>
-      <c r="B50" s="103" t="str">
+      <c r="B50" s="97" t="str">
         <f>master!B39</f>
         <v>ガバクラとは？</v>
       </c>
-      <c r="C50" s="53" t="str">
+      <c r="C50" s="50" t="str">
         <f>master!C39</f>
         <v>36．ガバメントクラウドとは？</v>
       </c>
-      <c r="D50" s="100" t="s">
-        <v>142</v>
-      </c>
-      <c r="E50" s="101"/>
-      <c r="F50" s="102"/>
-      <c r="G50" s="53" t="s">
-        <v>40</v>
+      <c r="D50" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" s="95"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="50" t="s">
+        <v>39</v>
       </c>
       <c r="H50" s="12"/>
-      <c r="I50" s="51" t="s">
+      <c r="I50" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J50" s="49">
+      <c r="J50" s="46">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K50" s="46"/>
+      <c r="K50" s="43"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" ht="176.4">
       <c r="A51" s="11"/>
-      <c r="B51" s="104"/>
-      <c r="C51" s="53" t="str">
+      <c r="B51" s="98"/>
+      <c r="C51" s="50" t="str">
         <f>master!C40</f>
         <v>37．ガバメントクラウド対象</v>
       </c>
-      <c r="D51" s="100" t="s">
-        <v>143</v>
-      </c>
-      <c r="E51" s="101"/>
-      <c r="F51" s="102"/>
-      <c r="G51" s="53" t="s">
-        <v>116</v>
+      <c r="D51" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="E51" s="95"/>
+      <c r="F51" s="96"/>
+      <c r="G51" s="50" t="s">
+        <v>115</v>
       </c>
       <c r="H51" s="12"/>
-      <c r="I51" s="51" t="s">
+      <c r="I51" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J51" s="49">
+      <c r="J51" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K51" s="46"/>
+      <c r="K51" s="43"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" ht="289.8">
       <c r="A52" s="11"/>
-      <c r="B52" s="104"/>
-      <c r="C52" s="53" t="str">
+      <c r="B52" s="98"/>
+      <c r="C52" s="50" t="str">
         <f>master!C41</f>
         <v>38．ガバナンスとセキュリティ</v>
       </c>
-      <c r="D52" s="100" t="s">
-        <v>144</v>
-      </c>
-      <c r="E52" s="101"/>
-      <c r="F52" s="102"/>
-      <c r="G52" s="53" t="s">
-        <v>118</v>
+      <c r="D52" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" s="95"/>
+      <c r="F52" s="96"/>
+      <c r="G52" s="50" t="s">
+        <v>117</v>
       </c>
       <c r="H52" s="12"/>
-      <c r="I52" s="51" t="s">
+      <c r="I52" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J52" s="49">
+      <c r="J52" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K52" s="46"/>
+      <c r="K52" s="43"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="189">
       <c r="A53" s="11"/>
-      <c r="B53" s="104"/>
-      <c r="C53" s="53" t="str">
+      <c r="B53" s="98"/>
+      <c r="C53" s="50" t="str">
         <f>master!C42</f>
         <v>39．ガバメントクラウドテンプレート</v>
       </c>
-      <c r="D53" s="100" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" s="101"/>
-      <c r="F53" s="102"/>
-      <c r="G53" s="53" t="s">
-        <v>52</v>
+      <c r="D53" s="94" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" s="95"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="50" t="s">
+        <v>51</v>
       </c>
       <c r="H53" s="12"/>
-      <c r="I53" s="51" t="s">
+      <c r="I53" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J53" s="49">
+      <c r="J53" s="46">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K53" s="46"/>
+      <c r="K53" s="43"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" ht="163.80000000000001">
       <c r="A54" s="11"/>
-      <c r="B54" s="104"/>
-      <c r="C54" s="53" t="str">
+      <c r="B54" s="98"/>
+      <c r="C54" s="50" t="str">
         <f>master!C43</f>
         <v>40．マネージドサービスの活用</v>
       </c>
-      <c r="D54" s="100" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" s="101"/>
-      <c r="F54" s="102"/>
-      <c r="G54" s="53" t="s">
-        <v>51</v>
+      <c r="D54" s="94" t="s">
+        <v>145</v>
+      </c>
+      <c r="E54" s="95"/>
+      <c r="F54" s="96"/>
+      <c r="G54" s="50" t="s">
+        <v>50</v>
       </c>
       <c r="H54" s="12"/>
-      <c r="I54" s="51" t="s">
+      <c r="I54" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J54" s="49">
+      <c r="J54" s="46">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K54" s="46"/>
+      <c r="K54" s="43"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="239.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="104"/>
-      <c r="C55" s="53" t="str">
+      <c r="B55" s="98"/>
+      <c r="C55" s="50" t="str">
         <f>master!C44</f>
         <v>41．リアーキテクチャとは？</v>
       </c>
-      <c r="D55" s="100" t="s">
-        <v>147</v>
-      </c>
-      <c r="E55" s="101"/>
-      <c r="F55" s="102"/>
-      <c r="G55" s="53" t="s">
-        <v>119</v>
+      <c r="D55" s="94" t="s">
+        <v>146</v>
+      </c>
+      <c r="E55" s="95"/>
+      <c r="F55" s="96"/>
+      <c r="G55" s="50" t="s">
+        <v>118</v>
       </c>
       <c r="H55" s="12"/>
-      <c r="I55" s="51" t="s">
+      <c r="I55" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J55" s="49">
+      <c r="J55" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K55" s="46"/>
+      <c r="K55" s="43"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="176.4">
       <c r="A56" s="11"/>
-      <c r="B56" s="104"/>
-      <c r="C56" s="53" t="str">
+      <c r="B56" s="98"/>
+      <c r="C56" s="50" t="str">
         <f>master!C45</f>
         <v>42．リアーキテクチャの重要性</v>
       </c>
-      <c r="D56" s="100" t="s">
-        <v>148</v>
-      </c>
-      <c r="E56" s="101"/>
-      <c r="F56" s="102"/>
-      <c r="G56" s="53" t="s">
-        <v>116</v>
+      <c r="D56" s="94" t="s">
+        <v>147</v>
+      </c>
+      <c r="E56" s="95"/>
+      <c r="F56" s="96"/>
+      <c r="G56" s="50" t="s">
+        <v>115</v>
       </c>
       <c r="H56" s="12"/>
-      <c r="I56" s="51" t="s">
+      <c r="I56" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J56" s="49">
+      <c r="J56" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K56" s="46"/>
+      <c r="K56" s="43"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="239.4">
       <c r="A57" s="11"/>
-      <c r="B57" s="104"/>
-      <c r="C57" s="53" t="str">
+      <c r="B57" s="98"/>
+      <c r="C57" s="50" t="str">
         <f>master!C46</f>
         <v>43．リアーキテクチャの実施プロセス</v>
       </c>
-      <c r="D57" s="100" t="s">
-        <v>149</v>
-      </c>
-      <c r="E57" s="101"/>
-      <c r="F57" s="102"/>
-      <c r="G57" s="53" t="s">
-        <v>119</v>
+      <c r="D57" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="E57" s="95"/>
+      <c r="F57" s="96"/>
+      <c r="G57" s="50" t="s">
+        <v>118</v>
       </c>
       <c r="H57" s="12"/>
-      <c r="I57" s="51" t="s">
+      <c r="I57" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J57" s="49">
+      <c r="J57" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K57" s="46"/>
+      <c r="K57" s="43"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="302.39999999999998">
       <c r="A58" s="11"/>
-      <c r="B58" s="104"/>
-      <c r="C58" s="53" t="str">
+      <c r="B58" s="98"/>
+      <c r="C58" s="50" t="str">
         <f>master!C47</f>
         <v>44．リアーキテクチャの手法</v>
       </c>
-      <c r="D58" s="100" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" s="101"/>
-      <c r="F58" s="102"/>
-      <c r="G58" s="53" t="s">
-        <v>125</v>
+      <c r="D58" s="94" t="s">
+        <v>151</v>
+      </c>
+      <c r="E58" s="95"/>
+      <c r="F58" s="96"/>
+      <c r="G58" s="50" t="s">
+        <v>124</v>
       </c>
       <c r="H58" s="12"/>
-      <c r="I58" s="51" t="s">
+      <c r="I58" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J58" s="49">
+      <c r="J58" s="46">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K58" s="46"/>
+      <c r="K58" s="43"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="25.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="104"/>
-      <c r="C59" s="53" t="str">
+      <c r="B59" s="98"/>
+      <c r="C59" s="50" t="str">
         <f>master!C48</f>
         <v>45．本講義のまとめ</v>
       </c>
-      <c r="D59" s="100" t="s">
-        <v>153</v>
-      </c>
-      <c r="E59" s="101"/>
-      <c r="F59" s="102"/>
-      <c r="G59" s="53" t="s">
-        <v>44</v>
+      <c r="D59" s="94" t="s">
+        <v>152</v>
+      </c>
+      <c r="E59" s="95"/>
+      <c r="F59" s="96"/>
+      <c r="G59" s="50" t="s">
+        <v>43</v>
       </c>
       <c r="H59" s="12"/>
-      <c r="I59" s="51" t="s">
+      <c r="I59" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J59" s="49">
+      <c r="J59" s="46">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K59" s="46"/>
+      <c r="K59" s="43"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="104"/>
-      <c r="C60" s="53" t="str">
+      <c r="B60" s="98"/>
+      <c r="C60" s="50" t="str">
         <f>master!C49</f>
         <v>46．AWS CDKの講師デモ</v>
       </c>
-      <c r="D60" s="100" t="s">
+      <c r="D60" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="E60" s="95"/>
+      <c r="F60" s="96"/>
+      <c r="G60" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="E60" s="101"/>
-      <c r="F60" s="102"/>
-      <c r="G60" s="53" t="s">
-        <v>151</v>
-      </c>
       <c r="H60" s="12"/>
-      <c r="I60" s="51" t="s">
+      <c r="I60" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="J60" s="46">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K60" s="43" t="s">
         <v>154</v>
-      </c>
-      <c r="J60" s="49">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K60" s="46" t="s">
-        <v>155</v>
       </c>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
@@ -4530,40 +4501,75 @@
     </row>
     <row r="61" spans="1:14" ht="88.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="105"/>
-      <c r="C61" s="53" t="str">
+      <c r="B61" s="99"/>
+      <c r="C61" s="50" t="str">
         <f>master!C50</f>
         <v>47．AWS 豆知識　【コラム】</v>
       </c>
-      <c r="D61" s="100" t="s">
-        <v>167</v>
-      </c>
-      <c r="E61" s="101"/>
-      <c r="F61" s="102"/>
-      <c r="G61" s="53" t="s">
-        <v>43</v>
+      <c r="D61" s="94" t="s">
+        <v>166</v>
+      </c>
+      <c r="E61" s="95"/>
+      <c r="F61" s="96"/>
+      <c r="G61" s="50" t="s">
+        <v>42</v>
       </c>
       <c r="H61" s="12"/>
-      <c r="I61" s="51" t="s">
+      <c r="I61" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="J61" s="46">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K61" s="43" t="s">
         <v>154</v>
-      </c>
-      <c r="J61" s="49">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K61" s="46" t="s">
-        <v>155</v>
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
+  <mergeCells count="61">
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B50:B61"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D59:F59"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="B15:B23"/>
@@ -4580,45 +4586,11 @@
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B50:B61"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4651,266 +4623,266 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="72" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="C24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="C35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
         <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="C40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="C44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/IG/AI Native-AWS_IG.xlsx
+++ b/IG/AI Native-AWS_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAF8102-2C2D-4E90-97FB-E3B4CD19EC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8D5239-AA68-4467-9C82-B10404A23FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -63,7 +63,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1687,7 +1687,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1970,6 +1970,15 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1987,21 +1996,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3003,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N61"/>
+  <dimension ref="A2:N60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3069,61 +3063,69 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
-    <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="30"/>
+    <row r="6" spans="1:14">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="B7" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="91"/>
+      <c r="F7" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="47"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="B8" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="91"/>
-      <c r="F8" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="47"/>
-      <c r="J8" s="6"/>
+      <c r="B8" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="44"/>
+      <c r="F8" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>19</v>
+      </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -3131,15 +3133,15 @@
     </row>
     <row r="9" spans="1:14">
       <c r="B9" s="34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="103" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="104"/>
+      <c r="E9" s="44"/>
       <c r="F9" s="36" t="s">
         <v>22</v>
       </c>
@@ -3153,15 +3155,15 @@
     </row>
     <row r="10" spans="1:14">
       <c r="B10" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="104"/>
+      <c r="E10" s="44"/>
       <c r="F10" s="36" t="s">
         <v>22</v>
       </c>
@@ -3173,122 +3175,127 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14">
-      <c r="B11" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="104"/>
-      <c r="F11" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="24" customHeight="1">
+    <row r="12" spans="1:14" ht="24" customHeight="1">
+      <c r="A12" s="10"/>
+      <c r="B12" s="85" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="95"/>
+      <c r="K12" s="84" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="10"/>
-      <c r="B13" s="85" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="85" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="85" t="s">
-        <v>8</v>
-      </c>
+      <c r="B13" s="85"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="85"/>
       <c r="F13" s="85"/>
-      <c r="G13" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="84" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="100" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="101"/>
-      <c r="K13" s="84" t="s">
-        <v>33</v>
-      </c>
+      <c r="G13" s="85"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="85"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" ht="88.2">
       <c r="A14" s="10"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="85"/>
+      <c r="B14" s="100" t="str">
+        <f>master!B4</f>
+        <v>クラウドとは？</v>
+      </c>
+      <c r="C14" s="50" t="str">
+        <f>master!C4</f>
+        <v>１．IT業界の歴史</v>
+      </c>
+      <c r="D14" s="97" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="46">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K14" s="43"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="88.2">
+    <row r="15" spans="1:14" ht="100.8">
       <c r="A15" s="10"/>
-      <c r="B15" s="97" t="str">
-        <f>master!B4</f>
-        <v>クラウドとは？</v>
-      </c>
+      <c r="B15" s="101"/>
       <c r="C15" s="50" t="str">
-        <f>master!C4</f>
-        <v>１．IT業界の歴史</v>
-      </c>
-      <c r="D15" s="94" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="95"/>
-      <c r="F15" s="96"/>
+        <f>master!C5</f>
+        <v>２．クラウドの市場価値向上</v>
+      </c>
+      <c r="D15" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
       <c r="G15" s="50" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="46">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K15" s="43"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="100.8">
-      <c r="A16" s="10"/>
-      <c r="B16" s="98"/>
+    <row r="16" spans="1:14" ht="138.6">
+      <c r="A16" s="11"/>
+      <c r="B16" s="101"/>
       <c r="C16" s="50" t="str">
-        <f>master!C5</f>
-        <v>２．クラウドの市場価値向上</v>
-      </c>
-      <c r="D16" s="94" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" s="95"/>
-      <c r="F16" s="96"/>
+        <f>master!C6</f>
+        <v>３．クラウドとは？</v>
+      </c>
+      <c r="D16" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="98"/>
+      <c r="F16" s="99"/>
       <c r="G16" s="50" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="48" t="s">
@@ -3302,20 +3309,20 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="138.6">
+    <row r="17" spans="1:14" ht="100.8">
       <c r="A17" s="11"/>
-      <c r="B17" s="98"/>
+      <c r="B17" s="101"/>
       <c r="C17" s="50" t="str">
-        <f>master!C6</f>
-        <v>３．クラウドとは？</v>
-      </c>
-      <c r="D17" s="94" t="s">
-        <v>157</v>
-      </c>
-      <c r="E17" s="95"/>
-      <c r="F17" s="96"/>
+        <f>master!C7</f>
+        <v>４．オンプレミスとのコスト比較</v>
+      </c>
+      <c r="D17" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="98"/>
+      <c r="F17" s="99"/>
       <c r="G17" s="50" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="48" t="s">
@@ -3329,74 +3336,74 @@
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="100.8">
+    <row r="18" spans="1:14" ht="201.6">
       <c r="A18" s="11"/>
-      <c r="B18" s="98"/>
+      <c r="B18" s="101"/>
       <c r="C18" s="50" t="str">
-        <f>master!C7</f>
-        <v>４．オンプレミスとのコスト比較</v>
-      </c>
-      <c r="D18" s="94" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18" s="95"/>
-      <c r="F18" s="96"/>
+        <f>master!C8</f>
+        <v>５．クラウドの特徴</v>
+      </c>
+      <c r="D18" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="98"/>
+      <c r="F18" s="99"/>
       <c r="G18" s="50" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J18" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K18" s="43"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" ht="201.6">
+    <row r="19" spans="1:14" ht="113.4">
       <c r="A19" s="11"/>
-      <c r="B19" s="98"/>
+      <c r="B19" s="101"/>
       <c r="C19" s="50" t="str">
-        <f>master!C8</f>
-        <v>５．クラウドの特徴</v>
-      </c>
-      <c r="D19" s="94" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="95"/>
-      <c r="F19" s="96"/>
+        <f>master!C9</f>
+        <v>６．クラウドの特徴2</v>
+      </c>
+      <c r="D19" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="98"/>
+      <c r="F19" s="99"/>
       <c r="G19" s="50" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="46">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K19" s="43"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="113.4">
+    <row r="20" spans="1:14" ht="151.19999999999999">
       <c r="A20" s="11"/>
-      <c r="B20" s="98"/>
+      <c r="B20" s="101"/>
       <c r="C20" s="50" t="str">
-        <f>master!C9</f>
-        <v>６．クラウドの特徴2</v>
-      </c>
-      <c r="D20" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="96"/>
+        <f>master!C10</f>
+        <v>７．アベイラビリティゾーンとリージョン</v>
+      </c>
+      <c r="D20" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="98"/>
+      <c r="F20" s="99"/>
       <c r="G20" s="50" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="48" t="s">
@@ -3410,104 +3417,104 @@
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="151.19999999999999">
+    <row r="21" spans="1:14" ht="100.8">
       <c r="A21" s="11"/>
-      <c r="B21" s="98"/>
+      <c r="B21" s="101"/>
       <c r="C21" s="50" t="str">
-        <f>master!C10</f>
-        <v>７．アベイラビリティゾーンとリージョン</v>
-      </c>
-      <c r="D21" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="95"/>
-      <c r="F21" s="96"/>
+        <f>master!C11</f>
+        <v>８．クラウドにおける責任共有モデル</v>
+      </c>
+      <c r="D21" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="98"/>
+      <c r="F21" s="99"/>
       <c r="G21" s="50" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K21" s="43"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="100.8">
+    <row r="22" spans="1:14" ht="37.799999999999997">
       <c r="A22" s="11"/>
-      <c r="B22" s="98"/>
+      <c r="B22" s="102"/>
       <c r="C22" s="50" t="str">
-        <f>master!C11</f>
-        <v>８．クラウドにおける責任共有モデル</v>
-      </c>
-      <c r="D22" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="95"/>
-      <c r="F22" s="96"/>
+        <f>master!C12</f>
+        <v>９．NTTデータはデータセンターが得意　【コラム】</v>
+      </c>
+      <c r="D22" s="97" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="98"/>
+      <c r="F22" s="99"/>
       <c r="G22" s="50" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J22" s="46">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K22" s="43"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="37.799999999999997">
+    <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="99"/>
+      <c r="B23" s="100" t="str">
+        <f>master!B13</f>
+        <v>AWSとは？</v>
+      </c>
       <c r="C23" s="50" t="str">
-        <f>master!C12</f>
-        <v>９．NTTデータはデータセンターが得意　【コラム】</v>
-      </c>
-      <c r="D23" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="95"/>
-      <c r="F23" s="96"/>
+        <f>master!C13</f>
+        <v>10．AWSとは？</v>
+      </c>
+      <c r="D23" s="97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="98"/>
+      <c r="F23" s="99"/>
       <c r="G23" s="50" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J23" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K23" s="43"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="75.599999999999994">
+    <row r="24" spans="1:14" ht="100.8">
       <c r="A24" s="11"/>
-      <c r="B24" s="97" t="str">
-        <f>master!B13</f>
-        <v>AWSとは？</v>
-      </c>
+      <c r="B24" s="101"/>
       <c r="C24" s="50" t="str">
-        <f>master!C13</f>
-        <v>10．AWSとは？</v>
-      </c>
-      <c r="D24" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="95"/>
-      <c r="F24" s="96"/>
+        <f>master!C14</f>
+        <v>11．AWSの利用産業</v>
+      </c>
+      <c r="D24" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="98"/>
+      <c r="F24" s="99"/>
       <c r="G24" s="50" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="48" t="s">
@@ -3521,74 +3528,74 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="100.8">
+    <row r="25" spans="1:14" ht="176.4">
       <c r="A25" s="11"/>
-      <c r="B25" s="98"/>
+      <c r="B25" s="101"/>
       <c r="C25" s="50" t="str">
-        <f>master!C14</f>
-        <v>11．AWSの利用産業</v>
-      </c>
-      <c r="D25" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="95"/>
-      <c r="F25" s="96"/>
+        <f>master!C15</f>
+        <v>12．Web3層アーキテクチャ</v>
+      </c>
+      <c r="D25" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="98"/>
+      <c r="F25" s="99"/>
       <c r="G25" s="50" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J25" s="46">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K25" s="43"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="176.4">
+    <row r="26" spans="1:14" ht="201.6">
       <c r="A26" s="11"/>
-      <c r="B26" s="98"/>
+      <c r="B26" s="101"/>
       <c r="C26" s="50" t="str">
-        <f>master!C15</f>
-        <v>12．Web3層アーキテクチャ</v>
-      </c>
-      <c r="D26" s="94" t="s">
-        <v>164</v>
-      </c>
-      <c r="E26" s="95"/>
-      <c r="F26" s="96"/>
+        <f>master!C16</f>
+        <v>13．AWSの基本アーキテクチャ</v>
+      </c>
+      <c r="D26" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="98"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="50" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J26" s="46">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K26" s="43"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="201.6">
+    <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="98"/>
+      <c r="B27" s="101"/>
       <c r="C27" s="50" t="str">
-        <f>master!C16</f>
-        <v>13．AWSの基本アーキテクチャ</v>
-      </c>
-      <c r="D27" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" s="95"/>
-      <c r="F27" s="96"/>
+        <f>master!C17</f>
+        <v>14．Amazon VPC（Virtual Private Cloud）</v>
+      </c>
+      <c r="D27" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" s="98"/>
+      <c r="F27" s="99"/>
       <c r="G27" s="50" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="48" t="s">
@@ -3602,20 +3609,20 @@
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="113.4">
+    <row r="28" spans="1:14" ht="138.6">
       <c r="A28" s="11"/>
-      <c r="B28" s="98"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="50" t="str">
-        <f>master!C17</f>
-        <v>14．Amazon VPC（Virtual Private Cloud）</v>
-      </c>
-      <c r="D28" s="94" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28" s="95"/>
-      <c r="F28" s="96"/>
+        <f>master!C18</f>
+        <v>15．Amazon EC2（Elastic Compute Cloud）</v>
+      </c>
+      <c r="D28" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="98"/>
+      <c r="F28" s="99"/>
       <c r="G28" s="50" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="48" t="s">
@@ -3629,20 +3636,20 @@
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="138.6">
+    <row r="29" spans="1:14" ht="189">
       <c r="A29" s="11"/>
-      <c r="B29" s="98"/>
+      <c r="B29" s="101"/>
       <c r="C29" s="50" t="str">
-        <f>master!C18</f>
-        <v>15．Amazon EC2（Elastic Compute Cloud）</v>
-      </c>
-      <c r="D29" s="94" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" s="95"/>
-      <c r="F29" s="96"/>
+        <f>master!C19</f>
+        <v>16．Amazon RDS（Relational Database Service）</v>
+      </c>
+      <c r="D29" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="98"/>
+      <c r="F29" s="99"/>
       <c r="G29" s="50" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="48" t="s">
@@ -3656,20 +3663,20 @@
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14" ht="189">
+    <row r="30" spans="1:14" ht="201.6">
       <c r="A30" s="11"/>
-      <c r="B30" s="98"/>
+      <c r="B30" s="101"/>
       <c r="C30" s="50" t="str">
-        <f>master!C19</f>
-        <v>16．Amazon RDS（Relational Database Service）</v>
-      </c>
-      <c r="D30" s="94" t="s">
-        <v>160</v>
-      </c>
-      <c r="E30" s="95"/>
-      <c r="F30" s="96"/>
+        <f>master!C20</f>
+        <v>17．マネージドサービスとは？</v>
+      </c>
+      <c r="D30" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="98"/>
+      <c r="F30" s="99"/>
       <c r="G30" s="50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="48" t="s">
@@ -3683,20 +3690,20 @@
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="201.6">
+    <row r="31" spans="1:14" ht="176.4">
       <c r="A31" s="11"/>
-      <c r="B31" s="98"/>
+      <c r="B31" s="101"/>
       <c r="C31" s="50" t="str">
-        <f>master!C20</f>
-        <v>17．マネージドサービスとは？</v>
-      </c>
-      <c r="D31" s="94" t="s">
-        <v>161</v>
-      </c>
-      <c r="E31" s="95"/>
-      <c r="F31" s="96"/>
+        <f>master!C21</f>
+        <v>18．ELB（Elastic Load Balancing）</v>
+      </c>
+      <c r="D31" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="98"/>
+      <c r="F31" s="99"/>
       <c r="G31" s="50" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="48" t="s">
@@ -3710,20 +3717,20 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="176.4">
+    <row r="32" spans="1:14" ht="214.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="98"/>
+      <c r="B32" s="101"/>
       <c r="C32" s="50" t="str">
-        <f>master!C21</f>
-        <v>18．ELB（Elastic Load Balancing）</v>
-      </c>
-      <c r="D32" s="94" t="s">
-        <v>162</v>
-      </c>
-      <c r="E32" s="95"/>
-      <c r="F32" s="96"/>
+        <f>master!C22</f>
+        <v>19．Amazon S3（Simple Storage Service）</v>
+      </c>
+      <c r="D32" s="97" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="98"/>
+      <c r="F32" s="99"/>
       <c r="G32" s="50" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="48" t="s">
@@ -3737,20 +3744,20 @@
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="214.2">
+    <row r="33" spans="1:14" ht="176.4">
       <c r="A33" s="11"/>
-      <c r="B33" s="98"/>
+      <c r="B33" s="101"/>
       <c r="C33" s="50" t="str">
-        <f>master!C22</f>
-        <v>19．Amazon S3（Simple Storage Service）</v>
-      </c>
-      <c r="D33" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="E33" s="95"/>
-      <c r="F33" s="96"/>
+        <f>master!C23</f>
+        <v>20．Amazon CloudWatch</v>
+      </c>
+      <c r="D33" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="98"/>
+      <c r="F33" s="99"/>
       <c r="G33" s="50" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="48" t="s">
@@ -3764,20 +3771,20 @@
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" ht="176.4">
+    <row r="34" spans="1:14" ht="239.4">
       <c r="A34" s="11"/>
-      <c r="B34" s="98"/>
+      <c r="B34" s="101"/>
       <c r="C34" s="50" t="str">
-        <f>master!C23</f>
-        <v>20．Amazon CloudWatch</v>
-      </c>
-      <c r="D34" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96"/>
+        <f>master!C24</f>
+        <v>21．コンピューティングサービス</v>
+      </c>
+      <c r="D34" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="98"/>
+      <c r="F34" s="99"/>
       <c r="G34" s="50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="48" t="s">
@@ -3791,47 +3798,47 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="239.4">
+    <row r="35" spans="1:14" ht="277.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="98"/>
+      <c r="B35" s="101"/>
       <c r="C35" s="50" t="str">
-        <f>master!C24</f>
-        <v>21．コンピューティングサービス</v>
-      </c>
-      <c r="D35" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" s="95"/>
-      <c r="F35" s="96"/>
+        <f>master!C25</f>
+        <v>22．コンテナとは？</v>
+      </c>
+      <c r="D35" s="97" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="98"/>
+      <c r="F35" s="99"/>
       <c r="G35" s="50" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J35" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K35" s="43"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="277.2">
+    <row r="36" spans="1:14" ht="327.60000000000002">
       <c r="A36" s="11"/>
-      <c r="B36" s="98"/>
+      <c r="B36" s="101"/>
       <c r="C36" s="50" t="str">
-        <f>master!C25</f>
-        <v>22．コンテナとは？</v>
-      </c>
-      <c r="D36" s="94" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="95"/>
-      <c r="F36" s="96"/>
+        <f>master!C26</f>
+        <v>23．Amazon ECS (Elastic Container Service)</v>
+      </c>
+      <c r="D36" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="98"/>
+      <c r="F36" s="99"/>
       <c r="G36" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="48" t="s">
@@ -3845,47 +3852,45 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="327.60000000000002">
+    <row r="37" spans="1:14" ht="126">
       <c r="A37" s="11"/>
-      <c r="B37" s="98"/>
+      <c r="B37" s="101"/>
       <c r="C37" s="50" t="str">
-        <f>master!C26</f>
-        <v>23．Amazon ECS (Elastic Container Service)</v>
-      </c>
-      <c r="D37" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" s="95"/>
-      <c r="F37" s="96"/>
+        <f>master!C27</f>
+        <v>24．AWS Lambda</v>
+      </c>
+      <c r="D37" s="97" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="98"/>
+      <c r="F37" s="99"/>
       <c r="G37" s="50" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J37" s="46">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K37" s="43"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" ht="126">
+    <row r="38" spans="1:14" ht="25.2">
       <c r="A38" s="11"/>
-      <c r="B38" s="98"/>
+      <c r="B38" s="102"/>
       <c r="C38" s="50" t="str">
-        <f>master!C27</f>
-        <v>24．AWS Lambda</v>
-      </c>
-      <c r="D38" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" s="95"/>
-      <c r="F38" s="96"/>
+        <f>master!C28</f>
+        <v>25．その他の周辺サービス</v>
+      </c>
+      <c r="D38" s="97"/>
+      <c r="E38" s="98"/>
+      <c r="F38" s="99"/>
       <c r="G38" s="50" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="48" t="s">
@@ -3899,18 +3904,23 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="25.2">
+    <row r="39" spans="1:14" ht="252">
       <c r="A39" s="11"/>
-      <c r="B39" s="99"/>
+      <c r="B39" s="100" t="str">
+        <f>master!B29</f>
+        <v>CDKとは？</v>
+      </c>
       <c r="C39" s="50" t="str">
-        <f>master!C28</f>
-        <v>25．その他の周辺サービス</v>
-      </c>
-      <c r="D39" s="94"/>
-      <c r="E39" s="95"/>
-      <c r="F39" s="96"/>
+        <f>master!C29</f>
+        <v>26．AWS、Azure、Google Cloudの違い　【コラム】</v>
+      </c>
+      <c r="D39" s="97" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" s="98"/>
+      <c r="F39" s="99"/>
       <c r="G39" s="50" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="48" t="s">
@@ -3924,77 +3934,74 @@
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="252">
+    <row r="40" spans="1:14" ht="189">
       <c r="A40" s="11"/>
-      <c r="B40" s="97" t="str">
-        <f>master!B29</f>
-        <v>CDKとは？</v>
-      </c>
+      <c r="B40" s="101"/>
       <c r="C40" s="50" t="str">
-        <f>master!C29</f>
-        <v>26．AWS、Azure、Google Cloudの違い　【コラム】</v>
-      </c>
-      <c r="D40" s="94" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" s="95"/>
-      <c r="F40" s="96"/>
+        <f>master!C30</f>
+        <v>27．Infrastructure as Code (IaC) とは？</v>
+      </c>
+      <c r="D40" s="97" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="98"/>
+      <c r="F40" s="99"/>
       <c r="G40" s="50" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J40" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K40" s="43"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="189">
+    <row r="41" spans="1:14" ht="226.8">
       <c r="A41" s="11"/>
-      <c r="B41" s="98"/>
+      <c r="B41" s="101"/>
       <c r="C41" s="50" t="str">
-        <f>master!C30</f>
-        <v>27．Infrastructure as Code (IaC) とは？</v>
-      </c>
-      <c r="D41" s="94" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" s="95"/>
-      <c r="F41" s="96"/>
+        <f>master!C31</f>
+        <v>28．IaCのメリット</v>
+      </c>
+      <c r="D41" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" s="98"/>
+      <c r="F41" s="99"/>
       <c r="G41" s="50" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J41" s="46">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K41" s="43"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="226.8">
+    <row r="42" spans="1:14" ht="239.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="98"/>
+      <c r="B42" s="101"/>
       <c r="C42" s="50" t="str">
-        <f>master!C31</f>
-        <v>28．IaCのメリット</v>
-      </c>
-      <c r="D42" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="E42" s="95"/>
-      <c r="F42" s="96"/>
+        <f>master!C32</f>
+        <v>29．IaCを実現するためのAWSサービス</v>
+      </c>
+      <c r="D42" s="97" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="98"/>
+      <c r="F42" s="99"/>
       <c r="G42" s="50" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="48" t="s">
@@ -4010,16 +4017,16 @@
     </row>
     <row r="43" spans="1:14" ht="239.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="98"/>
+      <c r="B43" s="101"/>
       <c r="C43" s="50" t="str">
-        <f>master!C32</f>
-        <v>29．IaCを実現するためのAWSサービス</v>
-      </c>
-      <c r="D43" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="95"/>
-      <c r="F43" s="96"/>
+        <f>master!C33</f>
+        <v>30．AWS CDKのメリット</v>
+      </c>
+      <c r="D43" s="97" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="98"/>
+      <c r="F43" s="99"/>
       <c r="G43" s="50" t="s">
         <v>118</v>
       </c>
@@ -4028,27 +4035,27 @@
         <v>25</v>
       </c>
       <c r="J43" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K43" s="43"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="239.4">
+    <row r="44" spans="1:14" ht="264.60000000000002">
       <c r="A44" s="11"/>
-      <c r="B44" s="98"/>
+      <c r="B44" s="101"/>
       <c r="C44" s="50" t="str">
-        <f>master!C33</f>
-        <v>30．AWS CDKのメリット</v>
-      </c>
-      <c r="D44" s="94" t="s">
-        <v>135</v>
-      </c>
-      <c r="E44" s="95"/>
-      <c r="F44" s="96"/>
+        <f>master!C34</f>
+        <v>31．AWS CDKの仕組み</v>
+      </c>
+      <c r="D44" s="97" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="98"/>
+      <c r="F44" s="99"/>
       <c r="G44" s="50" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="48" t="s">
@@ -4062,47 +4069,47 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="264.60000000000002">
+    <row r="45" spans="1:14" ht="100.8">
       <c r="A45" s="11"/>
-      <c r="B45" s="98"/>
+      <c r="B45" s="101"/>
       <c r="C45" s="50" t="str">
-        <f>master!C34</f>
-        <v>31．AWS CDKの仕組み</v>
-      </c>
-      <c r="D45" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" s="95"/>
-      <c r="F45" s="96"/>
+        <f>master!C35</f>
+        <v>32．AWS CloudFormationとの違い</v>
+      </c>
+      <c r="D45" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" s="98"/>
+      <c r="F45" s="99"/>
       <c r="G45" s="50" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J45" s="46">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K45" s="43"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="100.8">
+    <row r="46" spans="1:14" ht="163.80000000000001">
       <c r="A46" s="11"/>
-      <c r="B46" s="98"/>
+      <c r="B46" s="101"/>
       <c r="C46" s="50" t="str">
-        <f>master!C35</f>
-        <v>32．AWS CloudFormationとの違い</v>
-      </c>
-      <c r="D46" s="94" t="s">
-        <v>137</v>
-      </c>
-      <c r="E46" s="95"/>
-      <c r="F46" s="96"/>
+        <f>master!C36</f>
+        <v>33．クラウド移⾏時の7つの⽅式</v>
+      </c>
+      <c r="D46" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" s="98"/>
+      <c r="F46" s="99"/>
       <c r="G46" s="50" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="48" t="s">
@@ -4116,20 +4123,20 @@
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="163.80000000000001">
+    <row r="47" spans="1:14" ht="138.6">
       <c r="A47" s="11"/>
-      <c r="B47" s="98"/>
+      <c r="B47" s="101"/>
       <c r="C47" s="50" t="str">
-        <f>master!C36</f>
-        <v>33．クラウド移⾏時の7つの⽅式</v>
-      </c>
-      <c r="D47" s="94" t="s">
-        <v>138</v>
-      </c>
-      <c r="E47" s="95"/>
-      <c r="F47" s="96"/>
+        <f>master!C37</f>
+        <v>34．移行イメージ</v>
+      </c>
+      <c r="D47" s="97" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="98"/>
+      <c r="F47" s="99"/>
       <c r="G47" s="50" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="48" t="s">
@@ -4145,16 +4152,16 @@
     </row>
     <row r="48" spans="1:14" ht="138.6">
       <c r="A48" s="11"/>
-      <c r="B48" s="98"/>
+      <c r="B48" s="102"/>
       <c r="C48" s="50" t="str">
-        <f>master!C37</f>
-        <v>34．移行イメージ</v>
-      </c>
-      <c r="D48" s="94" t="s">
-        <v>139</v>
-      </c>
-      <c r="E48" s="95"/>
-      <c r="F48" s="96"/>
+        <f>master!C38</f>
+        <v>35．ReplatformとRefactorの比較</v>
+      </c>
+      <c r="D48" s="97" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" s="98"/>
+      <c r="F48" s="99"/>
       <c r="G48" s="50" t="s">
         <v>37</v>
       </c>
@@ -4170,77 +4177,77 @@
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="138.6">
+    <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="99"/>
+      <c r="B49" s="100" t="str">
+        <f>master!B39</f>
+        <v>ガバクラとは？</v>
+      </c>
       <c r="C49" s="50" t="str">
-        <f>master!C38</f>
-        <v>35．ReplatformとRefactorの比較</v>
-      </c>
-      <c r="D49" s="94" t="s">
-        <v>140</v>
-      </c>
-      <c r="E49" s="95"/>
-      <c r="F49" s="96"/>
+        <f>master!C39</f>
+        <v>36．ガバメントクラウドとは？</v>
+      </c>
+      <c r="D49" s="97" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="98"/>
+      <c r="F49" s="99"/>
       <c r="G49" s="50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J49" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K49" s="43"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="50.4">
+    <row r="50" spans="1:14" ht="176.4">
       <c r="A50" s="11"/>
-      <c r="B50" s="97" t="str">
-        <f>master!B39</f>
-        <v>ガバクラとは？</v>
-      </c>
+      <c r="B50" s="101"/>
       <c r="C50" s="50" t="str">
-        <f>master!C39</f>
-        <v>36．ガバメントクラウドとは？</v>
-      </c>
-      <c r="D50" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="E50" s="95"/>
-      <c r="F50" s="96"/>
+        <f>master!C40</f>
+        <v>37．ガバメントクラウド対象</v>
+      </c>
+      <c r="D50" s="97" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" s="98"/>
+      <c r="F50" s="99"/>
       <c r="G50" s="50" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J50" s="46">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K50" s="43"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="176.4">
+    <row r="51" spans="1:14" ht="289.8">
       <c r="A51" s="11"/>
-      <c r="B51" s="98"/>
+      <c r="B51" s="101"/>
       <c r="C51" s="50" t="str">
-        <f>master!C40</f>
-        <v>37．ガバメントクラウド対象</v>
-      </c>
-      <c r="D51" s="94" t="s">
-        <v>142</v>
-      </c>
-      <c r="E51" s="95"/>
-      <c r="F51" s="96"/>
+        <f>master!C41</f>
+        <v>38．ガバナンスとセキュリティ</v>
+      </c>
+      <c r="D51" s="97" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" s="98"/>
+      <c r="F51" s="99"/>
       <c r="G51" s="50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="48" t="s">
@@ -4254,47 +4261,47 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="289.8">
+    <row r="52" spans="1:14" ht="189">
       <c r="A52" s="11"/>
-      <c r="B52" s="98"/>
+      <c r="B52" s="101"/>
       <c r="C52" s="50" t="str">
-        <f>master!C41</f>
-        <v>38．ガバナンスとセキュリティ</v>
-      </c>
-      <c r="D52" s="94" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" s="95"/>
-      <c r="F52" s="96"/>
+        <f>master!C42</f>
+        <v>39．ガバメントクラウドテンプレート</v>
+      </c>
+      <c r="D52" s="97" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="98"/>
+      <c r="F52" s="99"/>
       <c r="G52" s="50" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J52" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K52" s="43"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14" ht="189">
+    <row r="53" spans="1:14" ht="163.80000000000001">
       <c r="A53" s="11"/>
-      <c r="B53" s="98"/>
+      <c r="B53" s="101"/>
       <c r="C53" s="50" t="str">
-        <f>master!C42</f>
-        <v>39．ガバメントクラウドテンプレート</v>
-      </c>
-      <c r="D53" s="94" t="s">
-        <v>144</v>
-      </c>
-      <c r="E53" s="95"/>
-      <c r="F53" s="96"/>
+        <f>master!C43</f>
+        <v>40．マネージドサービスの活用</v>
+      </c>
+      <c r="D53" s="97" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="98"/>
+      <c r="F53" s="99"/>
       <c r="G53" s="50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="48" t="s">
@@ -4308,47 +4315,47 @@
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:14" ht="163.80000000000001">
+    <row r="54" spans="1:14" ht="239.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="98"/>
+      <c r="B54" s="101"/>
       <c r="C54" s="50" t="str">
-        <f>master!C43</f>
-        <v>40．マネージドサービスの活用</v>
-      </c>
-      <c r="D54" s="94" t="s">
-        <v>145</v>
-      </c>
-      <c r="E54" s="95"/>
-      <c r="F54" s="96"/>
+        <f>master!C44</f>
+        <v>41．リアーキテクチャとは？</v>
+      </c>
+      <c r="D54" s="97" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="98"/>
+      <c r="F54" s="99"/>
       <c r="G54" s="50" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J54" s="46">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K54" s="43"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="1:14" ht="239.4">
+    <row r="55" spans="1:14" ht="176.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="98"/>
+      <c r="B55" s="101"/>
       <c r="C55" s="50" t="str">
-        <f>master!C44</f>
-        <v>41．リアーキテクチャとは？</v>
-      </c>
-      <c r="D55" s="94" t="s">
-        <v>146</v>
-      </c>
-      <c r="E55" s="95"/>
-      <c r="F55" s="96"/>
+        <f>master!C45</f>
+        <v>42．リアーキテクチャの重要性</v>
+      </c>
+      <c r="D55" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" s="98"/>
+      <c r="F55" s="99"/>
       <c r="G55" s="50" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="48" t="s">
@@ -4362,20 +4369,20 @@
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:14" ht="176.4">
+    <row r="56" spans="1:14" ht="239.4">
       <c r="A56" s="11"/>
-      <c r="B56" s="98"/>
+      <c r="B56" s="101"/>
       <c r="C56" s="50" t="str">
-        <f>master!C45</f>
-        <v>42．リアーキテクチャの重要性</v>
-      </c>
-      <c r="D56" s="94" t="s">
-        <v>147</v>
-      </c>
-      <c r="E56" s="95"/>
-      <c r="F56" s="96"/>
+        <f>master!C46</f>
+        <v>43．リアーキテクチャの実施プロセス</v>
+      </c>
+      <c r="D56" s="97" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" s="98"/>
+      <c r="F56" s="99"/>
       <c r="G56" s="50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="48" t="s">
@@ -4389,20 +4396,20 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="239.4">
+    <row r="57" spans="1:14" ht="302.39999999999998">
       <c r="A57" s="11"/>
-      <c r="B57" s="98"/>
+      <c r="B57" s="101"/>
       <c r="C57" s="50" t="str">
-        <f>master!C46</f>
-        <v>43．リアーキテクチャの実施プロセス</v>
-      </c>
-      <c r="D57" s="94" t="s">
-        <v>148</v>
-      </c>
-      <c r="E57" s="95"/>
-      <c r="F57" s="96"/>
+        <f>master!C47</f>
+        <v>44．リアーキテクチャの手法</v>
+      </c>
+      <c r="D57" s="97" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" s="98"/>
+      <c r="F57" s="99"/>
       <c r="G57" s="50" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="48" t="s">
@@ -4416,81 +4423,83 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="302.39999999999998">
+    <row r="58" spans="1:14" ht="25.2">
       <c r="A58" s="11"/>
-      <c r="B58" s="98"/>
+      <c r="B58" s="101"/>
       <c r="C58" s="50" t="str">
-        <f>master!C47</f>
-        <v>44．リアーキテクチャの手法</v>
-      </c>
-      <c r="D58" s="94" t="s">
-        <v>151</v>
-      </c>
-      <c r="E58" s="95"/>
-      <c r="F58" s="96"/>
+        <f>master!C48</f>
+        <v>45．本講義のまとめ</v>
+      </c>
+      <c r="D58" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" s="98"/>
+      <c r="F58" s="99"/>
       <c r="G58" s="50" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="48" t="s">
         <v>25</v>
       </c>
       <c r="J58" s="46">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K58" s="43"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="25.2">
+    <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="98"/>
+      <c r="B59" s="101"/>
       <c r="C59" s="50" t="str">
-        <f>master!C48</f>
-        <v>45．本講義のまとめ</v>
-      </c>
-      <c r="D59" s="94" t="s">
-        <v>152</v>
-      </c>
-      <c r="E59" s="95"/>
-      <c r="F59" s="96"/>
+        <f>master!C49</f>
+        <v>46．AWS CDKの講師デモ</v>
+      </c>
+      <c r="D59" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="E59" s="98"/>
+      <c r="F59" s="99"/>
       <c r="G59" s="50" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="48" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="J59" s="46">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K59" s="43"/>
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K59" s="43" t="s">
+        <v>154</v>
+      </c>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:14" ht="37.799999999999997">
+    <row r="60" spans="1:14" ht="88.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="98"/>
+      <c r="B60" s="102"/>
       <c r="C60" s="50" t="str">
-        <f>master!C49</f>
-        <v>46．AWS CDKの講師デモ</v>
-      </c>
-      <c r="D60" s="94" t="s">
-        <v>149</v>
-      </c>
-      <c r="E60" s="95"/>
-      <c r="F60" s="96"/>
+        <f>master!C50</f>
+        <v>47．AWS 豆知識　【コラム】</v>
+      </c>
+      <c r="D60" s="97" t="s">
+        <v>166</v>
+      </c>
+      <c r="E60" s="98"/>
+      <c r="F60" s="99"/>
       <c r="G60" s="50" t="s">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="H60" s="12"/>
       <c r="I60" s="48" t="s">
         <v>153</v>
       </c>
       <c r="J60" s="46">
-        <v>1.3888888888888888E-2</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K60" s="43" t="s">
         <v>154</v>
@@ -4499,82 +4508,19 @@
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:14" ht="88.2">
-      <c r="A61" s="11"/>
-      <c r="B61" s="99"/>
-      <c r="C61" s="50" t="str">
-        <f>master!C50</f>
-        <v>47．AWS 豆知識　【コラム】</v>
-      </c>
-      <c r="D61" s="94" t="s">
-        <v>166</v>
-      </c>
-      <c r="E61" s="95"/>
-      <c r="F61" s="96"/>
-      <c r="G61" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="H61" s="12"/>
-      <c r="I61" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="J61" s="46">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K61" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-    </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="B14:B22"/>
+    <mergeCell ref="B23:B38"/>
+    <mergeCell ref="B39:B48"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B50:B61"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B15:B23"/>
-    <mergeCell ref="B24:B39"/>
-    <mergeCell ref="B40:B49"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D32:F32"/>
@@ -4584,13 +4530,47 @@
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B49:B60"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D54:F54"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4603,7 +4583,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H15:H61</xm:sqref>
+          <xm:sqref>H14:H60</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
